--- a/セリフ編集/ナレーション・記事/称号・記録・年代記.xlsx
+++ b/セリフ編集/ナレーション・記事/称号・記録・年代記.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I459"/>
+  <dimension ref="A1:I447"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -8098,7 +8098,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[1].title</t>
+          <t xml:space="preserve">TRAIT_DEFS.華.desc</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8108,24 +8108,24 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[1].title</t>
+          <t xml:space="preserve">華.desc</t>
         </is>
       </c>
       <c r="G273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">8bit/RPG/オープニング「序・序曲」</t>
+          <t xml:space="preserve">集客力にボーナス。グッズ売上の重みも増加</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[1].artist</t>
+          <t xml:space="preserve">TRAIT_DEFS.ファンサービス.en</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8135,24 +8135,24 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[1].artist</t>
+          <t xml:space="preserve">ファンサービス.en</t>
         </is>
       </c>
       <c r="G274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MOMIZizm MUSiC（もみじば）</t>
+          <t xml:space="preserve">Fan Service</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[1].license</t>
+          <t xml:space="preserve">TRAIT_DEFS.ファンサービス.desc</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -8162,24 +8162,24 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[1].license</t>
+          <t xml:space="preserve">ファンサービス.desc</t>
         </is>
       </c>
       <c r="G275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー音楽素材</t>
+          <t xml:space="preserve">グッズ売上にボーナス。興行出場で人気が上がりやすい</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[2].title</t>
+          <t xml:space="preserve">TRAIT_DEFS.ヒール適性.en</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -8189,24 +8189,24 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[2].title</t>
+          <t xml:space="preserve">ヒール適性.en</t>
         </is>
       </c>
       <c r="G276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">RPG/感動のフィナーレ「エンディング・テーマ」</t>
+          <t xml:space="preserve">Heel Aptitude</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[2].artist</t>
+          <t xml:space="preserve">TRAIT_DEFS.ヒール適性.desc</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -8216,24 +8216,24 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[2].artist</t>
+          <t xml:space="preserve">ヒール適性.desc</t>
         </is>
       </c>
       <c r="G277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MOMIZizm MUSiC（もみじば）</t>
+          <t xml:space="preserve">悪役ムーブで人気を稼ぎ、因縁も生みやすい</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[2].license</t>
+          <t xml:space="preserve">TRAIT_DEFS.名勝負製造機.en</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -8243,24 +8243,24 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[2].license</t>
+          <t xml:space="preserve">名勝負製造機.en</t>
         </is>
       </c>
       <c r="G278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー音楽素材</t>
+          <t xml:space="preserve">Match Maker</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[3].license</t>
+          <t xml:space="preserve">TRAIT_DEFS.名勝負製造機.desc</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -8270,24 +8270,24 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[3].license</t>
+          <t xml:space="preserve">名勝負製造機.desc</t>
         </is>
       </c>
       <c r="G279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー音楽素材</t>
+          <t xml:space="preserve">試合がたまに大化けする。キックアウトやカウンターが生まれやすい</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[4].license</t>
+          <t xml:space="preserve">TRAIT_DEFS.引き出し上手.en</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -8297,24 +8297,24 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[4].license</t>
+          <t xml:space="preserve">引き出し上手.en</t>
         </is>
       </c>
       <c r="G280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー音楽素材</t>
+          <t xml:space="preserve">Best Bringer</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[5].artist</t>
+          <t xml:space="preserve">TRAIT_DEFS.引き出し上手.desc</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -8324,24 +8324,24 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[5].artist</t>
+          <t xml:space="preserve">引き出し上手.desc</t>
         </is>
       </c>
       <c r="G281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">岩城こん。</t>
+          <t xml:space="preserve">格下との試合でも質が下がりにくい</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[5].license</t>
+          <t xml:space="preserve">TRAIT_DEFS.ライバル体質.en</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -8351,24 +8351,24 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[5].license</t>
+          <t xml:space="preserve">ライバル体質.en</t>
         </is>
       </c>
       <c r="G282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー音楽素材</t>
+          <t xml:space="preserve">Rivalry Prone</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[6].artist</t>
+          <t xml:space="preserve">TRAIT_DEFS.ライバル体質.desc</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -8378,24 +8378,24 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[6].artist</t>
+          <t xml:space="preserve">ライバル体質.desc</t>
         </is>
       </c>
       <c r="G283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">岩城こん。</t>
+          <t xml:space="preserve">ライバル因縁が生まれやすい</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CREDITS.music[6].license</t>
+          <t xml:space="preserve">TRAIT_DEFS.早熟.en</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -8405,24 +8405,24 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CREDITS</t>
+          <t xml:space="preserve">TRAIT_DEFS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">music[6].license</t>
+          <t xml:space="preserve">早熟.en</t>
         </is>
       </c>
       <c r="G284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー音楽素材</t>
+          <t xml:space="preserve">Early Bloomer</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.華.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.早熟.desc</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -8437,19 +8437,19 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">華.desc</t>
+          <t xml:space="preserve">早熟.desc</t>
         </is>
       </c>
       <c r="G285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">集客力にボーナス。グッズ売上の重みも増加</t>
+          <t xml:space="preserve">10代から即戦力。20歳で完成するが、伸びしろは少ない</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ファンサービス.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.晩成.en</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -8464,19 +8464,19 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ファンサービス.en</t>
+          <t xml:space="preserve">晩成.en</t>
         </is>
       </c>
       <c r="G286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Fan Service</t>
+          <t xml:space="preserve">Late Bloomer</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ファンサービス.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.晩成.desc</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -8491,19 +8491,19 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ファンサービス.desc</t>
+          <t xml:space="preserve">晩成.desc</t>
         </is>
       </c>
       <c r="G287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グッズ売上にボーナス。興行出場で人気が上がりやすい</t>
+          <t xml:space="preserve">序盤は遅いが、21〜22歳でピークに成長する</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ヒール適性.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.遅咲き.en</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -8518,19 +8518,19 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ヒール適性.en</t>
+          <t xml:space="preserve">遅咲き.en</t>
         </is>
       </c>
       <c r="G288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Heel Aptitude</t>
+          <t xml:space="preserve">Late Starter</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ヒール適性.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.遅咲き.desc</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -8545,19 +8545,19 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ヒール適性.desc</t>
+          <t xml:space="preserve">遅咲き.desc</t>
         </is>
       </c>
       <c r="G289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪役ムーブで人気を稼ぎ、因縁も生みやすい</t>
+          <t xml:space="preserve">序盤は全く伸びないが、23歳で突然覚醒する</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.名勝負製造機.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.努力家.en</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -8572,19 +8572,19 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">名勝負製造機.en</t>
+          <t xml:space="preserve">努力家.en</t>
         </is>
       </c>
       <c r="G290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Match Maker</t>
+          <t xml:space="preserve">Hard Worker</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.名勝負製造機.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.努力家.desc</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -8599,19 +8599,19 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">名勝負製造機.desc</t>
+          <t xml:space="preserve">努力家.desc</t>
         </is>
       </c>
       <c r="G291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合がたまに大化けする。キックアウトやカウンターが生まれやすい</t>
+          <t xml:space="preserve">成長が安定しやすく、練習で体を壊しにくい</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.引き出し上手.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.破天荒.desc</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -8626,19 +8626,19 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">引き出し上手.en</t>
+          <t xml:space="preserve">破天荒.desc</t>
         </is>
       </c>
       <c r="G292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Best Bringer</t>
+          <t xml:space="preserve">成長にムラあり。爆発的か停滞</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.引き出し上手.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.適応力.desc</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -8653,19 +8653,19 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">引き出し上手.desc</t>
+          <t xml:space="preserve">適応力.desc</t>
         </is>
       </c>
       <c r="G293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格下との試合でも質が下がりにくい</t>
+          <t xml:space="preserve">怪我中でも成長が落ちにくく、追い込み練習にも強い</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ライバル体質.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.頑丈さ.desc</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -8680,19 +8680,19 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ライバル体質.en</t>
+          <t xml:space="preserve">頑丈さ.desc</t>
         </is>
       </c>
       <c r="G294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Rivalry Prone</t>
+          <t xml:space="preserve">怪我しにくい</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ライバル体質.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.ガラスの身体.en</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -8707,19 +8707,19 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ライバル体質.desc</t>
+          <t xml:space="preserve">ガラスの身体.en</t>
         </is>
       </c>
       <c r="G295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ライバル因縁が生まれやすい</t>
+          <t xml:space="preserve">Glass Body</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.早熟.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.ガラスの身体.desc</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -8734,19 +8734,19 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">早熟.en</t>
+          <t xml:space="preserve">ガラスの身体.desc</t>
         </is>
       </c>
       <c r="G296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Early Bloomer</t>
+          <t xml:space="preserve">怪我しやすいが、復帰のたびにファンの声援を集める</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.早熟.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.鉄人.en</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -8761,19 +8761,19 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">早熟.desc</t>
+          <t xml:space="preserve">鉄人.en</t>
         </is>
       </c>
       <c r="G297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">10代から即戦力。20歳で完成するが、伸びしろは少ない</t>
+          <t xml:space="preserve">Iron Man</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.晩成.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.鉄人.desc</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -8788,19 +8788,19 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">晩成.en</t>
+          <t xml:space="preserve">鉄人.desc</t>
         </is>
       </c>
       <c r="G298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Late Bloomer</t>
+          <t xml:space="preserve">コンディション全般に強い</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.晩成.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.不屈.desc</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -8815,19 +8815,19 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">晩成.desc</t>
+          <t xml:space="preserve">不屈.desc</t>
         </is>
       </c>
       <c r="G299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">序盤は遅いが、21〜22歳でピークに成長する</t>
+          <t xml:space="preserve">怪我からの復帰が速い</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.遅咲き.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.ムードメーカー.en</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -8842,19 +8842,19 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">遅咲き.en</t>
+          <t xml:space="preserve">ムードメーカー.en</t>
         </is>
       </c>
       <c r="G300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Late Starter</t>
+          <t xml:space="preserve">Mood Maker</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.遅咲き.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.ムードメーカー.desc</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -8869,19 +8869,19 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">遅咲き.desc</t>
+          <t xml:space="preserve">ムードメーカー.desc</t>
         </is>
       </c>
       <c r="G301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">序盤は全く伸びないが、23歳で突然覚醒する</t>
+          <t xml:space="preserve">明るさでロッカールームの空気を持ち上げる（雰囲気が良い時は効果が薄れる）</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.努力家.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.人望.desc</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -8896,19 +8896,19 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">努力家.en</t>
+          <t xml:space="preserve">人望.desc</t>
         </is>
       </c>
       <c r="G302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Hard Worker</t>
+          <t xml:space="preserve">不安定な選手たちの心を支える（不満が多い時ほど効果が大きい）</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.努力家.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.負けず嫌い.desc</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -8923,19 +8923,19 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">努力家.desc</t>
+          <t xml:space="preserve">負けず嫌い.desc</t>
         </is>
       </c>
       <c r="G303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">成長が安定しやすく、練習で体を壊しにくい</t>
+          <t xml:space="preserve">負けた翌週の練習成長にボーナス</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.破天荒.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.リーダー気質.desc</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -8950,19 +8950,19 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">破天荒.desc</t>
+          <t xml:space="preserve">リーダー気質.desc</t>
         </is>
       </c>
       <c r="G304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">成長にムラあり。爆発的か停滞</t>
+          <t xml:space="preserve">チームの不満を抑え、チャンピオン時は団体の顔として人気UP</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.適応力.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.忠誠心.desc</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -8977,19 +8977,19 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">適応力.desc</t>
+          <t xml:space="preserve">忠誠心.desc</t>
         </is>
       </c>
       <c r="G305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我中でも成長が落ちにくく、追い込み練習にも強い</t>
+          <t xml:space="preserve">引き抜きオファーが来る確率が大幅に低下</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.頑丈さ.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.野心.desc</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -9004,19 +9004,19 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">頑丈さ.desc</t>
+          <t xml:space="preserve">野心.desc</t>
         </is>
       </c>
       <c r="G306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我しにくい</t>
+          <t xml:space="preserve">タイトル挑戦時に試合が盛り上がり、覚醒しやすい</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ガラスの身体.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.番狂わせ体質.en</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -9031,19 +9031,19 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ガラスの身体.en</t>
+          <t xml:space="preserve">番狂わせ体質.en</t>
         </is>
       </c>
       <c r="G307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Glass Body</t>
+          <t xml:space="preserve">Upset Specialist</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ガラスの身体.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.番狂わせ体質.desc</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -9058,19 +9058,19 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ガラスの身体.desc</t>
+          <t xml:space="preserve">番狂わせ体質.desc</t>
         </is>
       </c>
       <c r="G308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我しやすいが、復帰のたびにファンの声援を集める</t>
+          <t xml:space="preserve">格上相手に丸め込み率UP</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.鉄人.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.闘志.en</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -9085,19 +9085,19 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">鉄人.en</t>
+          <t xml:space="preserve">闘志.en</t>
         </is>
       </c>
       <c r="G309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Iron Man</t>
+          <t xml:space="preserve">Fighting Spirit</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.鉄人.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.闘志.desc</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -9112,19 +9112,19 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">鉄人.desc</t>
+          <t xml:space="preserve">闘志.desc</t>
         </is>
       </c>
       <c r="G310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コンディション全般に強い</t>
+          <t xml:space="preserve">瀕死から粘る力が強く、負けても人気が落ちにくい</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.不屈.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.威圧感.desc</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -9139,19 +9139,19 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">不屈.desc</t>
+          <t xml:space="preserve">威圧感.desc</t>
         </is>
       </c>
       <c r="G311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我からの復帰が速い</t>
+          <t xml:space="preserve">対戦相手の序盤モメンタムが不利</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ムードメーカー.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.反骨心.desc</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -9166,343 +9166,343 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ムードメーカー.en</t>
+          <t xml:space="preserve">反骨心.desc</t>
         </is>
       </c>
       <c r="G312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Mood Maker</t>
+          <t xml:space="preserve">移籍願望が出やすいが、信頼が低いと成長する</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ムードメーカー.desc</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.striker</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ムードメーカー.desc</t>
+          <t xml:space="preserve">striker</t>
         </is>
       </c>
       <c r="G313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">明るさでロッカールームの空気を持ち上げる（雰囲気が良い時は効果が薄れる）</t>
+          <t xml:space="preserve">打撃</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.人望.desc</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.grappler</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">人望.desc</t>
+          <t xml:space="preserve">grappler</t>
         </is>
       </c>
       <c r="G314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不安定な選手たちの心を支える（不満が多い時ほど効果が大きい）</t>
+          <t xml:space="preserve">組技</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.負けず嫌い.desc</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.submission</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">負けず嫌い.desc</t>
+          <t xml:space="preserve">submission</t>
         </is>
       </c>
       <c r="G315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた翌週の練習成長にボーナス</t>
+          <t xml:space="preserve">関節技</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.リーダー気質.desc</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.brawler</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">リーダー気質.desc</t>
+          <t xml:space="preserve">brawler</t>
         </is>
       </c>
       <c r="G316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チームの不満を抑え、チャンピオン時は団体の顔として人気UP</t>
+          <t xml:space="preserve">喧嘩</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.忠誠心.desc</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.allround</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">忠誠心.desc</t>
+          <t xml:space="preserve">allround</t>
         </is>
       </c>
       <c r="G317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き抜きオファーが来る確率が大幅に低下</t>
+          <t xml:space="preserve">万能</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.野心.desc</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">野心.desc</t>
+          <t xml:space="preserve">early[1]</t>
         </is>
       </c>
       <c r="G318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトル挑戦時に試合が盛り上がり、覚醒しやすい</t>
+          <t xml:space="preserve">旗揚げ世代</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.番狂わせ体質.en</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">番狂わせ体質.en</t>
+          <t xml:space="preserve">early[2]</t>
         </is>
       </c>
       <c r="G319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Upset Specialist</t>
+          <t xml:space="preserve">創成期</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.番狂わせ体質.desc</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[3]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">番狂わせ体質.desc</t>
+          <t xml:space="preserve">early[3]</t>
         </is>
       </c>
       <c r="G320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格上相手に丸め込み率UP</t>
+          <t xml:space="preserve">始まりの灯</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.闘志.en</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[4]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">闘志.en</t>
+          <t xml:space="preserve">early[4]</t>
         </is>
       </c>
       <c r="G321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Fighting Spirit</t>
+          <t xml:space="preserve">旗を立てた日々</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.闘志.desc</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">闘志.desc</t>
+          <t xml:space="preserve">golden[1]</t>
         </is>
       </c>
       <c r="G322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">瀕死から粘る力が強く、負けても人気が落ちにくい</t>
+          <t xml:space="preserve">黄金期</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.威圧感.desc</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">威圧感.desc</t>
+          <t xml:space="preserve">golden[2]</t>
         </is>
       </c>
       <c r="G323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対戦相手の序盤モメンタムが不利</t>
+          <t xml:space="preserve">一強時代</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.反骨心.desc</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[3]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">反骨心.desc</t>
+          <t xml:space="preserve">golden[3]</t>
         </is>
       </c>
       <c r="G324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">移籍願望が出やすいが、信頼が低いと成長する</t>
+          <t xml:space="preserve">連続王者の時代</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.striker</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[4]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -9512,24 +9512,24 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">striker</t>
+          <t xml:space="preserve">golden[4]</t>
         </is>
       </c>
       <c r="G325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打撃</t>
+          <t xml:space="preserve">誰にも届かぬ高み</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.grappler</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -9539,24 +9539,24 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">grappler</t>
+          <t xml:space="preserve">almostThere[1]</t>
         </is>
       </c>
       <c r="G326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">組技</t>
+          <t xml:space="preserve">届かなかった頂</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.submission</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -9566,24 +9566,24 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">submission</t>
+          <t xml:space="preserve">almostThere[2]</t>
         </is>
       </c>
       <c r="G327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関節技</t>
+          <t xml:space="preserve">壁の前で</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.brawler</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[3]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -9593,24 +9593,24 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">brawler</t>
+          <t xml:space="preserve">almostThere[3]</t>
         </is>
       </c>
       <c r="G328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">喧嘩</t>
+          <t xml:space="preserve">頂を仰ぐ者たち</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.allround</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[4]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -9620,24 +9620,24 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">allround</t>
+          <t xml:space="preserve">almostThere[4]</t>
         </is>
       </c>
       <c r="G329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">万能</t>
+          <t xml:space="preserve">一歩、届かず</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[5]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -9652,19 +9652,19 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">early[1]</t>
+          <t xml:space="preserve">almostThere[5]</t>
         </is>
       </c>
       <c r="G330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">旗揚げ世代</t>
+          <t xml:space="preserve">影を踏んだ世代</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -9679,19 +9679,19 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">early[2]</t>
+          <t xml:space="preserve">challenge[1]</t>
         </is>
       </c>
       <c r="G331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">創成期</t>
+          <t xml:space="preserve">挑戦者世代</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -9706,19 +9706,19 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">early[3]</t>
+          <t xml:space="preserve">challenge[2]</t>
         </is>
       </c>
       <c r="G332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">始まりの灯</t>
+          <t xml:space="preserve">気鋭の時代</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[3]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -9733,19 +9733,19 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">early[4]</t>
+          <t xml:space="preserve">challenge[3]</t>
         </is>
       </c>
       <c r="G333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">旗を立てた日々</t>
+          <t xml:space="preserve">牙を研ぐ日々</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[4]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -9760,19 +9760,19 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">golden[1]</t>
+          <t xml:space="preserve">challenge[4]</t>
         </is>
       </c>
       <c r="G334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黄金期</t>
+          <t xml:space="preserve">壁にぶつかった世代</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -9787,19 +9787,19 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">golden[2]</t>
+          <t xml:space="preserve">idol[1]</t>
         </is>
       </c>
       <c r="G335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一強時代</t>
+          <t xml:space="preserve">華やかなる時代</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -9814,19 +9814,19 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">golden[3]</t>
+          <t xml:space="preserve">idol[2]</t>
         </is>
       </c>
       <c r="G336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連続王者の時代</t>
+          <t xml:space="preserve">熱気と歓声の時代</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[3]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -9841,19 +9841,19 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">golden[4]</t>
+          <t xml:space="preserve">idol[3]</t>
         </is>
       </c>
       <c r="G337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰にも届かぬ高み</t>
+          <t xml:space="preserve">ファン人気で支えた世代</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[4]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -9868,19 +9868,19 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[1]</t>
+          <t xml:space="preserve">idol[4]</t>
         </is>
       </c>
       <c r="G338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">届かなかった頂</t>
+          <t xml:space="preserve">華のある世代</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -9895,19 +9895,19 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[2]</t>
+          <t xml:space="preserve">enduring[1]</t>
         </is>
       </c>
       <c r="G339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁の前で</t>
+          <t xml:space="preserve">低迷期</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -9922,19 +9922,19 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[3]</t>
+          <t xml:space="preserve">enduring[2]</t>
         </is>
       </c>
       <c r="G340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂を仰ぐ者たち</t>
+          <t xml:space="preserve">日陰の奉仕者たち</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[3]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -9949,19 +9949,19 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[4]</t>
+          <t xml:space="preserve">enduring[3]</t>
         </is>
       </c>
       <c r="G341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一歩、届かず</t>
+          <t xml:space="preserve">灯を絶やさぬ者たち</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[5]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[4]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -9976,19 +9976,19 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[5]</t>
+          <t xml:space="preserve">enduring[4]</t>
         </is>
       </c>
       <c r="G342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">影を踏んだ世代</t>
+          <t xml:space="preserve">世代交代期</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -10003,19 +10003,19 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">challenge[1]</t>
+          <t xml:space="preserve">other[1]</t>
         </is>
       </c>
       <c r="G343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑戦者世代</t>
+          <t xml:space="preserve">中堅職人世代</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[2]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -10030,19 +10030,19 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">challenge[2]</t>
+          <t xml:space="preserve">other[2]</t>
         </is>
       </c>
       <c r="G344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気鋭の時代</t>
+          <t xml:space="preserve">残留組の時代</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[3]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -10057,19 +10057,19 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">challenge[3]</t>
+          <t xml:space="preserve">other[3]</t>
         </is>
       </c>
       <c r="G345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">牙を研ぐ日々</t>
+          <t xml:space="preserve">端境期</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[4]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -10084,19 +10084,19 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">challenge[4]</t>
+          <t xml:space="preserve">other[4]</t>
         </is>
       </c>
       <c r="G346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁にぶつかった世代</t>
+          <t xml:space="preserve">過渡期世代</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[1]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -10106,24 +10106,24 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">idol[1]</t>
+          <t xml:space="preserve">slight[1]</t>
         </is>
       </c>
       <c r="G347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">華やかなる時代</t>
+          <t xml:space="preserve">この世代は、{org}のスタイルを少しだけ{axis}寄りにした。</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[2]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[2]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -10133,24 +10133,24 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">idol[2]</t>
+          <t xml:space="preserve">slight[2]</t>
         </is>
       </c>
       <c r="G348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱気と歓声の時代</t>
+          <t xml:space="preserve">{org}の試合内容に{axis}の傾向が少し混じり始めた。</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[3]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[3]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -10160,24 +10160,24 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">idol[3]</t>
+          <t xml:space="preserve">slight[3]</t>
         </is>
       </c>
       <c r="G349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファン人気で支えた世代</t>
+          <t xml:space="preserve">この世代は{org}に{axis}の傾向をわずかに残した。</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[4]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[4]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -10187,24 +10187,24 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">idol[4]</t>
+          <t xml:space="preserve">slight[4]</t>
         </is>
       </c>
       <c r="G350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">華のある世代</t>
+          <t xml:space="preserve">{org}の基本路線に{axis}の要素が少し加わった。</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[1]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -10214,24 +10214,24 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enduring[1]</t>
+          <t xml:space="preserve">moderate[1]</t>
         </is>
       </c>
       <c r="G351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">低迷期</t>
+          <t xml:space="preserve">この世代は{org}のスタイルに{axis}色を残した。</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[2]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[2]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -10241,24 +10241,24 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enduring[2]</t>
+          <t xml:space="preserve">moderate[2]</t>
         </is>
       </c>
       <c r="G352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日陰の奉仕者たち</t>
+          <t xml:space="preserve">{axis}中心の試合運びが、{org}全体の傾向を少し変えた。</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[3]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[3]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -10268,24 +10268,24 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enduring[3]</t>
+          <t xml:space="preserve">moderate[3]</t>
         </is>
       </c>
       <c r="G353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">灯を絶やさぬ者たち</t>
+          <t xml:space="preserve">次世代の選手は{axis}を一つの基準として育っていった。</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[4]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[4]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -10295,24 +10295,24 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enduring[4]</t>
+          <t xml:space="preserve">moderate[4]</t>
         </is>
       </c>
       <c r="G354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世代交代期</t>
+          <t xml:space="preserve">{org}が{axis}を団体の特色として語れるようになったのは、この世代からだった。</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[1]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -10322,24 +10322,24 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">other[1]</t>
+          <t xml:space="preserve">strong[1]</t>
         </is>
       </c>
       <c r="G355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">中堅職人世代</t>
+          <t xml:space="preserve">この世代を経て、{org}のスタイルは{axis}色が明確になった。</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[2]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[2]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -10349,24 +10349,24 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">other[2]</t>
+          <t xml:space="preserve">strong[2]</t>
         </is>
       </c>
       <c r="G356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残留組の時代</t>
+          <t xml:space="preserve">この世代以降、{org}の若手は{axis}を基本として選ぶようになった。</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[3]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[3]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -10376,24 +10376,24 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">other[3]</t>
+          <t xml:space="preserve">strong[3]</t>
         </is>
       </c>
       <c r="G357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">端境期</t>
+          <t xml:space="preserve">{axis}が{org}の代名詞として定着した時期だった。</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[4]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[4]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -10403,24 +10403,24 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">other[4]</t>
+          <t xml:space="preserve">strong[4]</t>
         </is>
       </c>
       <c r="G358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">過渡期世代</t>
+          <t xml:space="preserve">この世代以降、{org}の主流は{axis}に移った。</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[1]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -10430,24 +10430,24 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">slight[1]</t>
+          <t xml:space="preserve">peakDefender[1]</t>
         </is>
       </c>
       <c r="G359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代は、{org}のスタイルを少しだけ{axis}寄りにした。</t>
+          <t xml:space="preserve">{surname}は章を通じて{defenses}度の防衛を積み上げ、団体の中心軸であり続けた。</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[2]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -10457,24 +10457,24 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">slight[2]</t>
+          <t xml:space="preserve">peakDefender[2]</t>
         </is>
       </c>
       <c r="G360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{org}の試合内容に{axis}の傾向が少し混じり始めた。</t>
+          <t xml:space="preserve">挑戦者を{defenses}度退けた{surname}は、この章の屋台骨だった。</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[3]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -10484,24 +10484,24 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">slight[3]</t>
+          <t xml:space="preserve">peakDefender[3]</t>
         </is>
       </c>
       <c r="G361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代は{org}に{axis}の傾向をわずかに残した。</t>
+          <t xml:space="preserve">{defenses}度防衛——{surname}が王座にいる時間が、この世代の輪郭を形作った。</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[4]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -10511,24 +10511,24 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">slight[4]</t>
+          <t xml:space="preserve">peakDefender[4]</t>
         </is>
       </c>
       <c r="G362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{org}の基本路線に{axis}の要素が少し加わった。</t>
+          <t xml:space="preserve">{defenses}度の防衛を重ねた{surname}は、団体の絶対的な軸として君臨した。</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -10538,24 +10538,24 @@
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[1]</t>
+          <t xml:space="preserve">defender[1]</t>
         </is>
       </c>
       <c r="G363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代は{org}のスタイルに{axis}色を残した。</t>
+          <t xml:space="preserve">{surname}は王座を{defenses}度防衛し、団体の核として時代を背負った。</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[2]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -10565,24 +10565,24 @@
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[2]</t>
+          <t xml:space="preserve">defender[2]</t>
         </is>
       </c>
       <c r="G364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{axis}中心の試合運びが、{org}全体の傾向を少し変えた。</t>
+          <t xml:space="preserve">{titleReigns}度の戴冠と{defenses}度の防衛。{surname}が立っていることが、団体の安定そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[3]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -10592,24 +10592,24 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[3]</t>
+          <t xml:space="preserve">defender[3]</t>
         </is>
       </c>
       <c r="G365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次世代の選手は{axis}を一つの基準として育っていった。</t>
+          <t xml:space="preserve">{surname}は王座を離さなかった。挑戦者たちはなかなか手が届かなかった。</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[4]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -10619,24 +10619,24 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[4]</t>
+          <t xml:space="preserve">defender[4]</t>
         </is>
       </c>
       <c r="G366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{org}が{axis}を団体の特色として語れるようになったのは、この世代からだった。</t>
+          <t xml:space="preserve">{surname}の{defenses}度の防衛は、この章の屋台骨だった。</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -10646,24 +10646,24 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">strong[1]</t>
+          <t xml:space="preserve">champion[1]</t>
         </is>
       </c>
       <c r="G367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代を経て、{org}のスタイルは{axis}色が明確になった。</t>
+          <t xml:space="preserve">{surname}は{titleReigns}度の戴冠を経て、この章の主役を担った。</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[2]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -10673,24 +10673,24 @@
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">strong[2]</t>
+          <t xml:space="preserve">champion[2]</t>
         </is>
       </c>
       <c r="G368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代以降、{org}の若手は{axis}を基本として選ぶようになった。</t>
+          <t xml:space="preserve">{titleReigns}度の戴冠を重ねた{surname}は、この世代の中心人物の一人だった。</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[3]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -10700,24 +10700,24 @@
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">strong[3]</t>
+          <t xml:space="preserve">champion[3]</t>
         </is>
       </c>
       <c r="G369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{axis}が{org}の代名詞として定着した時期だった。</t>
+          <t xml:space="preserve">何度王座から落ちても、{surname}は戻ってきた。{titleReigns}度の戴冠はその粘りの証だった。</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[4]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -10727,24 +10727,24 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">strong[4]</t>
+          <t xml:space="preserve">champion[4]</t>
         </is>
       </c>
       <c r="G370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代以降、{org}の主流は{axis}に移った。</t>
+          <t xml:space="preserve">{titleReigns}度の戴冠を通じて、{surname}はこの章の流れを作った。</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -10759,19 +10759,19 @@
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender[1]</t>
+          <t xml:space="preserve">popStar[1]</t>
         </is>
       </c>
       <c r="G371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は章を通じて{defenses}度の防衛を積み上げ、団体の中心軸であり続けた。</t>
+          <t xml:space="preserve">{surname}の人気が客足を支えた。戦績ではなく動員で、時代を作った世代だった。</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[2]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -10786,19 +10786,19 @@
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender[2]</t>
+          <t xml:space="preserve">popStar[2]</t>
         </is>
       </c>
       <c r="G372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑戦者を{defenses}度退けた{surname}は、この章の屋台骨だった。</t>
+          <t xml:space="preserve">王座にこそ恵まれなかったが、{surname}の華やかさが客席を埋めた。</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[3]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -10813,19 +10813,19 @@
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender[3]</t>
+          <t xml:space="preserve">popStar[3]</t>
         </is>
       </c>
       <c r="G373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{defenses}度防衛——{surname}が王座にいる時間が、この世代の輪郭を形作った。</t>
+          <t xml:space="preserve">試合記録には残らない記憶というものを、{surname}は、その人気でこの世代に刻みつけた。</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[4]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -10840,19 +10840,19 @@
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender[4]</t>
+          <t xml:space="preserve">popStar[4]</t>
         </is>
       </c>
       <c r="G374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{defenses}度の防衛を重ねた{surname}は、団体の絶対的な軸として君臨した。</t>
+          <t xml:space="preserve">{surname}を見るために客が会場に押し寄せた。それがこの世代の正体だった。</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[1]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -10867,19 +10867,19 @@
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender[1]</t>
+          <t xml:space="preserve">generationShift[1]</t>
         </is>
       </c>
       <c r="G375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は王座を{defenses}度防衛し、団体の核として時代を背負った。</t>
+          <t xml:space="preserve">{surname}は前世代の主役たちと並走し、世代交代の橋渡しとなった。</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[2]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -10894,19 +10894,19 @@
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender[2]</t>
+          <t xml:space="preserve">generationShift[2]</t>
         </is>
       </c>
       <c r="G376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{titleReigns}度の戴冠と{defenses}度の防衛。{surname}が立っていることが、団体の安定そのものだった。</t>
+          <t xml:space="preserve">{surname}の章は、過去と未来が混じり合った時間として団体史に残る。</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[3]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -10921,19 +10921,19 @@
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender[3]</t>
+          <t xml:space="preserve">generationShift[3]</t>
         </is>
       </c>
       <c r="G377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は王座を離さなかった。挑戦者たちはなかなか手が届かなかった。</t>
+          <t xml:space="preserve">前章の主役たちが退いていく中、{surname}が次の中心を担った。</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[4]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -10948,19 +10948,19 @@
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender[4]</t>
+          <t xml:space="preserve">generationShift[4]</t>
         </is>
       </c>
       <c r="G378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の{defenses}度の防衛は、この章の屋台骨だった。</t>
+          <t xml:space="preserve">{surname}は古参と新参の間に立ち、団体の世代を繋いだ。</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[1]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -10975,19 +10975,19 @@
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion[1]</t>
+          <t xml:space="preserve">struggle[1]</t>
         </is>
       </c>
       <c r="G379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{titleReigns}度の戴冠を経て、この章の主役を担った。</t>
+          <t xml:space="preserve">{surname}は{styleJa}を貫いたが、上位の壁は厚かった。届かないまま章は閉じる。</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[2]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -11002,19 +11002,19 @@
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion[2]</t>
+          <t xml:space="preserve">struggle[2]</t>
         </is>
       </c>
       <c r="G380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{titleReigns}度の戴冠を重ねた{surname}は、この世代の中心人物の一人だった。</t>
+          <t xml:space="preserve">挑んでは敗れ、それでも{surname}は{styleJa}を捨てなかった。届かなかった世代の象徴である。</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[3]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -11029,19 +11029,19 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion[3]</t>
+          <t xml:space="preserve">struggle[3]</t>
         </is>
       </c>
       <c r="G381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度王座から落ちても、{surname}は戻ってきた。{titleReigns}度の戴冠はその粘りの証だった。</t>
+          <t xml:space="preserve">{surname}の章は、勝てなかった日々の記録である。だが、それでも諦めず挑戦を続けた日々の記録でもある。</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[4]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -11056,19 +11056,19 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion[4]</t>
+          <t xml:space="preserve">struggle[4]</t>
         </is>
       </c>
       <c r="G382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{titleReigns}度の戴冠を通じて、{surname}はこの章の流れを作った。</t>
+          <t xml:space="preserve">{surname}は何度も上位に挑み、何度も敗れた。それでも立ち上がり続けた世代だった。</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -11083,19 +11083,19 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar[1]</t>
+          <t xml:space="preserve">craftsman[1]</t>
         </is>
       </c>
       <c r="G383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の人気が客足を支えた。戦績ではなく動員で、時代を作った世代だった。</t>
+          <t xml:space="preserve">{surname}は{styleJa}を武器に団体を支えた。王座にこそ届かなかったが、世代の支柱だった。</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[2]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -11110,19 +11110,19 @@
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar[2]</t>
+          <t xml:space="preserve">craftsman[2]</t>
         </is>
       </c>
       <c r="G384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座にこそ恵まれなかったが、{surname}の華やかさが客席を埋めた。</t>
+          <t xml:space="preserve">OVR{peakOVR}に達した{surname}は、無冠ながら誰よりも信頼される選手だった。</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[3]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -11137,19 +11137,19 @@
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar[3]</t>
+          <t xml:space="preserve">craftsman[3]</t>
         </is>
       </c>
       <c r="G385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合記録には残らない記憶というものを、{surname}は、その人気でこの世代に刻みつけた。</t>
+          <t xml:space="preserve">{surname}の{styleJa}は派手さこそないが、団体を底から支え続けた。</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[4]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -11164,19 +11164,19 @@
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar[4]</t>
+          <t xml:space="preserve">craftsman[4]</t>
         </is>
       </c>
       <c r="G386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}を見るために客が会場に押し寄せた。それがこの世代の正体だった。</t>
+          <t xml:space="preserve">王座とは縁がなかったが、{surname}の{styleJa}はこの章の地力そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[1]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -11191,19 +11191,19 @@
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift[1]</t>
+          <t xml:space="preserve">uncrowned[1]</t>
         </is>
       </c>
       <c r="G387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は前世代の主役たちと並走し、世代交代の橋渡しとなった。</t>
+          <t xml:space="preserve">{surname}は無冠ながらこの世代の主役だった。タイトルでは測れない存在感がそこにあった。</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[2]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -11218,19 +11218,19 @@
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift[2]</t>
+          <t xml:space="preserve">uncrowned[2]</t>
         </is>
       </c>
       <c r="G388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章は、過去と未来が混じり合った時間として団体史に残る。</t>
+          <t xml:space="preserve">王座を獲ることはなかったが、{surname}抜きにこの章は語れない。</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[3]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -11245,19 +11245,19 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift[3]</t>
+          <t xml:space="preserve">uncrowned[3]</t>
         </is>
       </c>
       <c r="G389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前章の主役たちが退いていく中、{surname}が次の中心を担った。</t>
+          <t xml:space="preserve">{surname}は最後までベルトを巻かなかった。だが団体史はこの選手を主役として記憶する。</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[4]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -11272,19 +11272,19 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift[4]</t>
+          <t xml:space="preserve">uncrowned[4]</t>
         </is>
       </c>
       <c r="G390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は古参と新参の間に立ち、団体の世代を繋いだ。</t>
+          <t xml:space="preserve">記録には残らないが、記憶には深く残る。{surname}はそういう世代の主役だった。</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[1]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -11294,24 +11294,24 @@
       </c>
       <c r="C391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle[1]</t>
+          <t xml:space="preserve">sectionA[1]</t>
         </is>
       </c>
       <c r="G391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{styleJa}を貫いたが、上位の壁は厚かった。届かないまま章は閉じる。</t>
+          <t xml:space="preserve">{surname1}と{surname2}は二枚看板としてこの章の主役を担った。{topRivalClause}{warClause}</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[2]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -11321,24 +11321,24 @@
       </c>
       <c r="C392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle[2]</t>
+          <t xml:space="preserve">sectionA[2]</t>
         </is>
       </c>
       <c r="G392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑んでは敗れ、それでも{surname}は{styleJa}を捨てなかった。届かなかった世代の象徴である。</t>
+          <t xml:space="preserve">{surname1}と{surname2}が並走したこの章は、二人の名前なしには語れない。{topVenueClause}</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[3]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -11348,24 +11348,24 @@
       </c>
       <c r="C393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle[3]</t>
+          <t xml:space="preserve">sectionA[3]</t>
         </is>
       </c>
       <c r="G393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章は、勝てなかった日々の記録である。だが、それでも諦めず挑戦を続けた日々の記録でもある。</t>
+          <t xml:space="preserve">王座とリングの中心を{surname1}と{surname2}が分け合い、団体は二つの頂を持つ時代に入った。</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[1]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -11375,24 +11375,24 @@
       </c>
       <c r="C394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle[4]</t>
+          <t xml:space="preserve">sectionB[1]</t>
         </is>
       </c>
       <c r="G394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は何度も上位に挑み、何度も敗れた。それでも立ち上がり続けた世代だった。</t>
+          <t xml:space="preserve">二人が引っ張った時代、{org}全体の試合運びには{spiritAxis}の色が濃く染み込んでいった。</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[2]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -11402,24 +11402,24 @@
       </c>
       <c r="C395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman[1]</t>
+          <t xml:space="preserve">sectionB[2]</t>
         </is>
       </c>
       <c r="G395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{styleJa}を武器に団体を支えた。王座にこそ届かなかったが、世代の支柱だった。</t>
+          <t xml:space="preserve">{eraTag}と呼ばれるこの章で、{surname1}と{surname2}はそれぞれ別の頂点を立てた。</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[3]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -11429,24 +11429,24 @@
       </c>
       <c r="C396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman[2]</t>
+          <t xml:space="preserve">sectionB[3]</t>
         </is>
       </c>
       <c r="G396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR{peakOVR}に達した{surname}は、無冠ながら誰よりも信頼される選手だった。</t>
+          <t xml:space="preserve">OVR と人気の双方で団体を支えた二人の在位は、{eraTag}そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[1]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -11456,24 +11456,24 @@
       </c>
       <c r="C397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman[3]</t>
+          <t xml:space="preserve">sectionC[1]</t>
         </is>
       </c>
       <c r="G397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の{styleJa}は派手さこそないが、団体を底から支え続けた。</t>
+          <t xml:space="preserve">二人が走り抜けた後、次章の主役{nextChapterTopSurname}が立ち上がる足場ができていた。</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[2]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -11483,24 +11483,24 @@
       </c>
       <c r="C398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman[4]</t>
+          <t xml:space="preserve">sectionC[2]</t>
         </is>
       </c>
       <c r="G398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座とは縁がなかったが、{surname}の{styleJa}はこの章の地力そのものだった。</t>
+          <t xml:space="preserve">{surname1}と{surname2}が並走した時代の余熱は、{risingPeerSurname}ら次世代に継がれた。</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[3]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -11510,24 +11510,24 @@
       </c>
       <c r="C399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned[1]</t>
+          <t xml:space="preserve">sectionC[3]</t>
         </is>
       </c>
       <c r="G399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は無冠ながらこの世代の主役だった。タイトルでは測れない存在感がそこにあった。</t>
+          <t xml:space="preserve">二つの頂が並んだこの章が閉じるとき、団体には{successorStyle}を継ぐ若手の影が伸び始めていた。</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionA[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -11537,24 +11537,24 @@
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned[2]</t>
+          <t xml:space="preserve">peakDefender.sectionA[1]</t>
         </is>
       </c>
       <c r="G400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座を獲ることはなかったが、{surname}抜きにこの章は語れない。</t>
+          <t xml:space="preserve">{surname}はこの章を通じて王座を{defenses}度防衛した。{topRivalClause}{topVenueClause}</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionA[2]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -11564,24 +11564,24 @@
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned[3]</t>
+          <t xml:space="preserve">peakDefender.sectionA[2]</t>
         </is>
       </c>
       <c r="G401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は最後までベルトを巻かなかった。だが団体史はこの選手を主役として記憶する。</t>
+          <t xml:space="preserve">{titleReigns}度の戴冠、{defenses}度の防衛——{surname}は挑戦者を退け続けた。{warClause}</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionB[1]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -11591,24 +11591,24 @@
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned[4]</t>
+          <t xml:space="preserve">peakDefender.sectionB[1]</t>
         </is>
       </c>
       <c r="G402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">記録には残らないが、記憶には深く残る。{surname}はそういう世代の主役だった。</t>
+          <t xml:space="preserve">{surname}が{styleJa}で団体を引っ張った時期、{org}全体の試合運びには{spiritAxis}の色が濃く染み込んでいった。</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionB[2]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -11618,24 +11618,24 @@
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionA[1]</t>
+          <t xml:space="preserve">peakDefender.sectionB[2]</t>
         </is>
       </c>
       <c r="G403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname1}と{surname2}は二枚看板としてこの章の主役を担った。{topRivalClause}{warClause}</t>
+          <t xml:space="preserve">OVR{peakOVR}・人気{peakPop}に達したこの選手の在位は、{eraTag}と呼ぶに相応しい時代を作った。</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionC[1]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -11645,24 +11645,24 @@
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionA[2]</t>
+          <t xml:space="preserve">peakDefender.sectionC[1]</t>
         </is>
       </c>
       <c r="G404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname1}と{surname2}が並走したこの章は、二人の名前なしには語れない。{topVenueClause}</t>
+          <t xml:space="preserve">{surname}が見せた{styleJa}は、{risingClause}次章の主役{nextChapterTopSurname}が立ち上がる足場は、確かにこの世代に築かれていた。</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionC[2]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -11672,24 +11672,24 @@
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionA[3]</t>
+          <t xml:space="preserve">peakDefender.sectionC[2]</t>
         </is>
       </c>
       <c r="G405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座とリングの中心を{surname1}と{surname2}が分け合い、団体は二つの頂を持つ時代に入った。</t>
+          <t xml:space="preserve">{surname}の章が閉じるとき、団体には{successorStyle}を継ぐ若手の影が既に伸び始めていた。</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionA[1]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -11699,24 +11699,24 @@
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionB[1]</t>
+          <t xml:space="preserve">defender.sectionA[1]</t>
         </is>
       </c>
       <c r="G406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人が引っ張った時代、{org}全体の試合運びには{spiritAxis}の色が濃く染み込んでいった。</t>
+          <t xml:space="preserve">{surname}は王座を{defenses}度防衛し、{titleReigns}度の戴冠と合わせて団体の核を担った。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionA[2]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -11726,24 +11726,24 @@
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionB[2]</t>
+          <t xml:space="preserve">defender.sectionA[2]</t>
         </is>
       </c>
       <c r="G407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{eraTag}と呼ばれるこの章で、{surname1}と{surname2}はそれぞれ別の頂点を立てた。</t>
+          <t xml:space="preserve">{surname}が立っていることが、団体の安定そのものだった。挑戦者たちはなかなか手が届かなかった。{warClause}</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionB[1]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -11753,24 +11753,24 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionB[3]</t>
+          <t xml:space="preserve">defender.sectionB[1]</t>
         </is>
       </c>
       <c r="G408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR と人気の双方で団体を支えた二人の在位は、{eraTag}そのものだった。</t>
+          <t xml:space="preserve">{surname}の{styleJa}は、この章の{org}を{spiritAxis}に染め上げた。</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionB[2]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -11780,24 +11780,24 @@
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionC[1]</t>
+          <t xml:space="preserve">defender.sectionB[2]</t>
         </is>
       </c>
       <c r="G409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人が走り抜けた後、次章の主役{nextChapterTopSurname}が立ち上がる足場ができていた。</t>
+          <t xml:space="preserve">{eraTag}と呼ばれるこの時代、戴冠者の名前を聞かれれば誰もが{surname}の名を挙げた。</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionC[1]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -11807,24 +11807,24 @@
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionC[2]</t>
+          <t xml:space="preserve">defender.sectionC[1]</t>
         </is>
       </c>
       <c r="G410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname1}と{surname2}が並走した時代の余熱は、{risingPeerSurname}ら次世代に継がれた。</t>
+          <t xml:space="preserve">{risingClause}{surname}の積み上げた防衛は、後進にとっての到達目標になった。</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionC[2]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -11834,24 +11834,24 @@
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionC[3]</t>
+          <t xml:space="preserve">defender.sectionC[2]</t>
         </is>
       </c>
       <c r="G411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二つの頂が並んだこの章が閉じるとき、団体には{successorStyle}を継ぐ若手の影が伸び始めていた。</t>
+          <t xml:space="preserve">{nextChapterTopSurname}が立つ前提として、{surname}が築いた地盤があった。</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionA[1]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -11866,19 +11866,19 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionA[1]</t>
+          <t xml:space="preserve">champion.sectionA[1]</t>
         </is>
       </c>
       <c r="G412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}はこの章を通じて王座を{defenses}度防衛した。{topRivalClause}{topVenueClause}</t>
+          <t xml:space="preserve">{surname}は{titleReigns}度の戴冠を重ね、この章の主役を担った。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionA[2]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -11893,19 +11893,19 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionA[2]</t>
+          <t xml:space="preserve">champion.sectionA[2]</t>
         </is>
       </c>
       <c r="G413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{titleReigns}度の戴冠、{defenses}度の防衛——{surname}は挑戦者を退け続けた。{warClause}</t>
+          <t xml:space="preserve">何度王座から落ちても、{surname}は戻ってきた。{titleReigns}度の戴冠はその粘りの証だった。{warClause}</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionB[1]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -11920,19 +11920,19 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionB[1]</t>
+          <t xml:space="preserve">champion.sectionB[1]</t>
         </is>
       </c>
       <c r="G414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が{styleJa}で団体を引っ張った時期、{org}全体の試合運びには{spiritAxis}の色が濃く染み込んでいった。</t>
+          <t xml:space="preserve">{surname}を中心に、{org}は{spiritAxis}の色を強めた章だった。</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionB[2]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -11947,19 +11947,19 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionB[2]</t>
+          <t xml:space="preserve">champion.sectionB[2]</t>
         </is>
       </c>
       <c r="G415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR{peakOVR}・人気{peakPop}に達したこの選手の在位は、{eraTag}と呼ぶに相応しい時代を作った。</t>
+          <t xml:space="preserve">OVR{peakOVR}の{surname}が立った時代、それは{eraTag}に他ならなかった。</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionC[1]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -11974,19 +11974,19 @@
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionC[1]</t>
+          <t xml:space="preserve">champion.sectionC[1]</t>
         </is>
       </c>
       <c r="G416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が見せた{styleJa}は、{risingClause}次章の主役{nextChapterTopSurname}が立ち上がる足場は、確かにこの世代に築かれていた。</t>
+          <t xml:space="preserve">{surname}が背中で見せた挑み続ける姿勢は、{risingPeerSurname}たち次世代の選手に受け継がれた。</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionC[2]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -12001,19 +12001,19 @@
       </c>
       <c r="D417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionC[2]</t>
+          <t xml:space="preserve">champion.sectionC[2]</t>
         </is>
       </c>
       <c r="G417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章が閉じるとき、団体には{successorStyle}を継ぐ若手の影が既に伸び始めていた。</t>
+          <t xml:space="preserve">{nextChapterTopSurname}の足場は、この章の{surname}の戴冠の積み重ねの上に立った。</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionA[1]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -12028,19 +12028,19 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionA[1]</t>
+          <t xml:space="preserve">popStar.sectionA[1]</t>
         </is>
       </c>
       <c r="G418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は王座を{defenses}度防衛し、{titleReigns}度の戴冠と合わせて団体の核を担った。{topRivalClause}</t>
+          <t xml:space="preserve">{surname}の人気が客足を支えた。戦績ではなく動員で、時代を作った世代だった。{topVenueClause}</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionA[2]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -12055,19 +12055,19 @@
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionA[2]</t>
+          <t xml:space="preserve">popStar.sectionA[2]</t>
         </is>
       </c>
       <c r="G419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が立っていることが、団体の安定そのものだった。挑戦者たちはなかなか手が届かなかった。{warClause}</t>
+          <t xml:space="preserve">王座にこそ恵まれなかったが、{surname}の華やかさが客席を埋めた。</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionB[1]</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -12082,19 +12082,19 @@
       </c>
       <c r="D420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionB[1]</t>
+          <t xml:space="preserve">popStar.sectionB[1]</t>
         </is>
       </c>
       <c r="G420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の{styleJa}は、この章の{org}を{spiritAxis}に染め上げた。</t>
+          <t xml:space="preserve">人気{peakPop}を記録したこの選手は、{org}にとってチケットそのものだった。</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionB[2]</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -12109,19 +12109,19 @@
       </c>
       <c r="D421" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionB[2]</t>
+          <t xml:space="preserve">popStar.sectionB[2]</t>
         </is>
       </c>
       <c r="G421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{eraTag}と呼ばれるこの時代、戴冠者の名前を聞かれれば誰もが{surname}の名を挙げた。</t>
+          <t xml:space="preserve">試合記録には残らない記憶というものを、{surname}は、その人気でこの世代に刻みつけた。</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionC[1]</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -12136,19 +12136,19 @@
       </c>
       <c r="D422" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionC[1]</t>
+          <t xml:space="preserve">popStar.sectionC[1]</t>
         </is>
       </c>
       <c r="G422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{risingClause}{surname}の積み上げた防衛は、後進にとっての到達目標になった。</t>
+          <t xml:space="preserve">{surname}が築いた華やぎの記憶は、{risingPeerSurname}たち次世代の客寄せにも引き継がれた。</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionC[2]</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -12163,19 +12163,19 @@
       </c>
       <c r="D423" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionC[2]</t>
+          <t xml:space="preserve">popStar.sectionC[2]</t>
         </is>
       </c>
       <c r="G423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nextChapterTopSurname}が立つ前提として、{surname}が築いた地盤があった。</t>
+          <t xml:space="preserve">{surname}が会場を埋めた時代の余熱は、次の章の{nextChapterTopSurname}の入場にも残っていた。</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionA[1]</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -12190,19 +12190,19 @@
       </c>
       <c r="D424" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionA[1]</t>
+          <t xml:space="preserve">generationShift.sectionA[1]</t>
         </is>
       </c>
       <c r="G424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{titleReigns}度の戴冠を重ね、この章の主役を担った。{topRivalClause}</t>
+          <t xml:space="preserve">{surname}は前世代の主役たちと並走し、世代交代の橋渡しとなった。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionA[2]</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -12217,19 +12217,19 @@
       </c>
       <c r="D425" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionA[2]</t>
+          <t xml:space="preserve">generationShift.sectionA[2]</t>
         </is>
       </c>
       <c r="G425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度王座から落ちても、{surname}は戻ってきた。{titleReigns}度の戴冠はその粘りの証だった。{warClause}</t>
+          <t xml:space="preserve">前章の主役たちが退いていく中、{surname}が次の中心を担った。</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionB[1]</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -12244,19 +12244,19 @@
       </c>
       <c r="D426" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionB[1]</t>
+          <t xml:space="preserve">generationShift.sectionB[1]</t>
         </is>
       </c>
       <c r="G426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}を中心に、{org}は{spiritAxis}の色を強めた章だった。</t>
+          <t xml:space="preserve">{surname}の章は、過去と未来が混じり合った時間として{org}史に残る。{eraTag}と呼ぶには複雑な時代だった。</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionB[2]</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
@@ -12271,19 +12271,19 @@
       </c>
       <c r="D427" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionB[2]</t>
+          <t xml:space="preserve">generationShift.sectionB[2]</t>
         </is>
       </c>
       <c r="G427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR{peakOVR}の{surname}が立った時代、それは{eraTag}に他ならなかった。</t>
+          <t xml:space="preserve">{spiritAxis}の地力を保ったまま、団体は次世代へと足場を移し始めていた。</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionC[1]</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
@@ -12298,19 +12298,19 @@
       </c>
       <c r="D428" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionC[1]</t>
+          <t xml:space="preserve">generationShift.sectionC[1]</t>
         </is>
       </c>
       <c r="G428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が背中で見せた挑み続ける姿勢は、{risingPeerSurname}たち次世代の選手に受け継がれた。</t>
+          <t xml:space="preserve">{risingClause}{surname}が橋渡した先に、次章の{nextChapterTopSurname}が立った。</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionC[2]</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
@@ -12325,19 +12325,19 @@
       </c>
       <c r="D429" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionC[2]</t>
+          <t xml:space="preserve">generationShift.sectionC[2]</t>
         </is>
       </c>
       <c r="G429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nextChapterTopSurname}の足場は、この章の{surname}の戴冠の積み重ねの上に立った。</t>
+          <t xml:space="preserve">{surname}が古参と新参の間に立った時間は、団体の世代の連続性そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionA[1]</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -12352,19 +12352,19 @@
       </c>
       <c r="D430" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionA[1]</t>
+          <t xml:space="preserve">struggle.sectionA[1]</t>
         </is>
       </c>
       <c r="G430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の人気が客足を支えた。戦績ではなく動員で、時代を作った世代だった。{topVenueClause}</t>
+          <t xml:space="preserve">{surname}は{styleJa}を貫いたが、上位の壁は厚かった。届かないまま章は閉じる。{warClause}</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionA[2]</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -12379,19 +12379,19 @@
       </c>
       <c r="D431" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionA[2]</t>
+          <t xml:space="preserve">struggle.sectionA[2]</t>
         </is>
       </c>
       <c r="G431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座にこそ恵まれなかったが、{surname}の華やかさが客席を埋めた。</t>
+          <t xml:space="preserve">挑んでは敗れ、それでも{surname}は{styleJa}を捨てなかった。</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionB[1]</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -12406,19 +12406,19 @@
       </c>
       <c r="D432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionB[1]</t>
+          <t xml:space="preserve">struggle.sectionB[1]</t>
         </is>
       </c>
       <c r="G432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">人気{peakPop}を記録したこの選手は、{org}にとってチケットそのものだった。</t>
+          <t xml:space="preserve">{surname}の章は、勝てなかった日々の記録である。だが、それでも諦めず挑戦を続けた日々の記録でもある。</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionB[2]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -12433,19 +12433,19 @@
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionB[2]</t>
+          <t xml:space="preserve">struggle.sectionB[2]</t>
         </is>
       </c>
       <c r="G433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合記録には残らない記憶というものを、{surname}は、その人気でこの世代に刻みつけた。</t>
+          <t xml:space="preserve">届かなかった世代の象徴として、{surname}は{org}の地力に深い陰影を残した。</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionC[1]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -12460,19 +12460,19 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionC[1]</t>
+          <t xml:space="preserve">struggle.sectionC[1]</t>
         </is>
       </c>
       <c r="G434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が築いた華やぎの記憶は、{risingPeerSurname}たち次世代の客寄せにも引き継がれた。</t>
+          <t xml:space="preserve">{surname}が届かなかった頂は、{risingPeerSurname}ら次世代の目標として残された。</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionC[2]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -12487,19 +12487,19 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionC[2]</t>
+          <t xml:space="preserve">struggle.sectionC[2]</t>
         </is>
       </c>
       <c r="G435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が会場を埋めた時代の余熱は、次の章の{nextChapterTopSurname}の入場にも残っていた。</t>
+          <t xml:space="preserve">{nextChapterTopSurname}が登る山は、{surname}が手を伸ばし続けた山だった。</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionA[1]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -12514,19 +12514,19 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionA[1]</t>
+          <t xml:space="preserve">craftsman.sectionA[1]</t>
         </is>
       </c>
       <c r="G436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は前世代の主役たちと並走し、世代交代の橋渡しとなった。{topRivalClause}</t>
+          <t xml:space="preserve">{surname}は{styleJa}を武器に団体を支えた。王座にこそ届かなかったが、世代の支柱だった。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionA[2]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -12541,19 +12541,19 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionA[2]</t>
+          <t xml:space="preserve">craftsman.sectionA[2]</t>
         </is>
       </c>
       <c r="G437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前章の主役たちが退いていく中、{surname}が次の中心を担った。</t>
+          <t xml:space="preserve">OVR{peakOVR}に達した{surname}は、無冠ながら誰よりも信頼される選手だった。</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionB[1]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -12568,19 +12568,19 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionB[1]</t>
+          <t xml:space="preserve">craftsman.sectionB[1]</t>
         </is>
       </c>
       <c r="G438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章は、過去と未来が混じり合った時間として{org}史に残る。{eraTag}と呼ぶには複雑な時代だった。</t>
+          <t xml:space="preserve">{surname}の{styleJa}は派手さこそないが、{org}を底から支え続けた。</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionB[2]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -12595,19 +12595,19 @@
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionB[2]</t>
+          <t xml:space="preserve">craftsman.sectionB[2]</t>
         </is>
       </c>
       <c r="G439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{spiritAxis}の地力を保ったまま、団体は次世代へと足場を移し始めていた。</t>
+          <t xml:space="preserve">王座とは縁がなかったが、{surname}の{styleJa}はこの章の地力そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionC[1]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -12622,19 +12622,19 @@
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionC[1]</t>
+          <t xml:space="preserve">craftsman.sectionC[1]</t>
         </is>
       </c>
       <c r="G440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{risingClause}{surname}が橋渡した先に、次章の{nextChapterTopSurname}が立った。</t>
+          <t xml:space="preserve">{surname}が継いだ{styleJa}の系譜は、{risingPeerSurname}ら次世代にも残った。</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionC[2]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -12649,19 +12649,19 @@
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionC[2]</t>
+          <t xml:space="preserve">craftsman.sectionC[2]</t>
         </is>
       </c>
       <c r="G441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が古参と新参の間に立った時間は、団体の世代の連続性そのものだった。</t>
+          <t xml:space="preserve">{nextChapterTopSurname}が前に出るとき、その背後には{surname}の積み上げた{styleJa}があった。</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionA[1]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -12676,19 +12676,19 @@
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionA[1]</t>
+          <t xml:space="preserve">uncrowned.sectionA[1]</t>
         </is>
       </c>
       <c r="G442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{styleJa}を貫いたが、上位の壁は厚かった。届かないまま章は閉じる。{warClause}</t>
+          <t xml:space="preserve">{surname}は無冠ながらこの世代の主役だった。タイトルでは測れない存在感がそこにあった。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionA[2]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -12703,19 +12703,19 @@
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionA[2]</t>
+          <t xml:space="preserve">uncrowned.sectionA[2]</t>
         </is>
       </c>
       <c r="G443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑んでは敗れ、それでも{surname}は{styleJa}を捨てなかった。</t>
+          <t xml:space="preserve">王座を獲ることはなかったが、{surname}抜きにこの章は語れない。</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionB[1]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -12730,19 +12730,19 @@
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionB[1]</t>
+          <t xml:space="preserve">uncrowned.sectionB[1]</t>
         </is>
       </c>
       <c r="G444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章は、勝てなかった日々の記録である。だが、それでも諦めず挑戦を続けた日々の記録でもある。</t>
+          <t xml:space="preserve">{surname}は最後までベルトを巻かなかった。だが{org}史はこの選手を主役として記憶する。</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionB[2]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -12757,19 +12757,19 @@
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionB[2]</t>
+          <t xml:space="preserve">uncrowned.sectionB[2]</t>
         </is>
       </c>
       <c r="G445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">届かなかった世代の象徴として、{surname}は{org}の地力に深い陰影を残した。</t>
+          <t xml:space="preserve">記録には残らないが、記憶には深く残る。{surname}はそういう世代の主役だった。</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionC[1]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -12784,19 +12784,19 @@
       </c>
       <c r="D446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionC[1]</t>
+          <t xml:space="preserve">uncrowned.sectionC[1]</t>
         </is>
       </c>
       <c r="G446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が届かなかった頂は、{risingPeerSurname}ら次世代の目標として残された。</t>
+          <t xml:space="preserve">{risingClause}{surname}の存在感は、無冠であることの強さとして次世代に伝わった。</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionC[2]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -12811,341 +12811,17 @@
       </c>
       <c r="D447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionC[2]</t>
+          <t xml:space="preserve">uncrowned.sectionC[2]</t>
         </is>
       </c>
       <c r="G447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nextChapterTopSurname}が登る山は、{surname}が手を伸ばし続けた山だった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="448" ht="40" customHeight="1">
-      <c r="A448" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionA[1]</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">craftsman.sectionA[1]</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{surname}は{styleJa}を武器に団体を支えた。王座にこそ届かなかったが、世代の支柱だった。{topRivalClause}</t>
-        </is>
-      </c>
-    </row>
-    <row r="449" ht="40" customHeight="1">
-      <c r="A449" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionA[2]</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">craftsman.sectionA[2]</t>
-        </is>
-      </c>
-      <c r="G449" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">OVR{peakOVR}に達した{surname}は、無冠ながら誰よりも信頼される選手だった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="450" ht="40" customHeight="1">
-      <c r="A450" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionB[1]</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">craftsman.sectionB[1]</t>
-        </is>
-      </c>
-      <c r="G450" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{surname}の{styleJa}は派手さこそないが、{org}を底から支え続けた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="451" ht="40" customHeight="1">
-      <c r="A451" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionB[2]</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">craftsman.sectionB[2]</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">王座とは縁がなかったが、{surname}の{styleJa}はこの章の地力そのものだった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="452" ht="40" customHeight="1">
-      <c r="A452" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionC[1]</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">craftsman.sectionC[1]</t>
-        </is>
-      </c>
-      <c r="G452" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{surname}が継いだ{styleJa}の系譜は、{risingPeerSurname}ら次世代にも残った。</t>
-        </is>
-      </c>
-    </row>
-    <row r="453" ht="40" customHeight="1">
-      <c r="A453" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionC[2]</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">craftsman.sectionC[2]</t>
-        </is>
-      </c>
-      <c r="G453" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{nextChapterTopSurname}が前に出るとき、その背後には{surname}の積み上げた{styleJa}があった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="454" ht="40" customHeight="1">
-      <c r="A454" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionA[1]</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">uncrowned.sectionA[1]</t>
-        </is>
-      </c>
-      <c r="G454" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{surname}は無冠ながらこの世代の主役だった。タイトルでは測れない存在感がそこにあった。{topRivalClause}</t>
-        </is>
-      </c>
-    </row>
-    <row r="455" ht="40" customHeight="1">
-      <c r="A455" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionA[2]</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">uncrowned.sectionA[2]</t>
-        </is>
-      </c>
-      <c r="G455" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">王座を獲ることはなかったが、{surname}抜きにこの章は語れない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="456" ht="40" customHeight="1">
-      <c r="A456" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionB[1]</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">uncrowned.sectionB[1]</t>
-        </is>
-      </c>
-      <c r="G456" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{surname}は最後までベルトを巻かなかった。だが{org}史はこの選手を主役として記憶する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="457" ht="40" customHeight="1">
-      <c r="A457" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionB[2]</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">uncrowned.sectionB[2]</t>
-        </is>
-      </c>
-      <c r="G457" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">記録には残らないが、記憶には深く残る。{surname}はそういう世代の主役だった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="458" ht="40" customHeight="1">
-      <c r="A458" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionC[1]</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">uncrowned.sectionC[1]</t>
-        </is>
-      </c>
-      <c r="G458" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{risingClause}{surname}の存在感は、無冠であることの強さとして次世代に伝わった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="459" ht="40" customHeight="1">
-      <c r="A459" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionC[2]</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">uncrowned.sectionC[2]</t>
-        </is>
-      </c>
-      <c r="G459" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">{nextChapterTopSurname}が王座を獲るとき、{surname}が残した「無冠の重み」が背後に静かに横たわっていた。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I459"/>
+  <autoFilter ref="A1:I447"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/ナレーション・記事/称号・記録・年代記.xlsx
+++ b/セリフ編集/ナレーション・記事/称号・記録・年代記.xlsx
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal._default[1]</t>
+          <t xml:space="preserve">rookie._default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -288,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -303,7 +303,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal._default[2]</t>
+          <t xml:space="preserve">rookie._default.normal[2]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="5">
@@ -320,7 +320,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.bold[1]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold._default[1]</t>
+          <t xml:space="preserve">rookie._default.bold[1]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="6">
@@ -352,7 +352,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.bold[2]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold._default[2]</t>
+          <t xml:space="preserve">rookie._default.bold[2]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="6">
@@ -384,7 +384,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.quiet._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.quiet[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.quiet._default[1]</t>
+          <t xml:space="preserve">rookie._default.quiet[1]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="7">
@@ -416,7 +416,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.shy._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.shy[1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.shy._default[1]</t>
+          <t xml:space="preserve">rookie._default.shy[1]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="8">
@@ -448,7 +448,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing._default[1]</t>
+          <t xml:space="preserve">rookie._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="9">
@@ -480,7 +480,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing._default[2]</t>
+          <t xml:space="preserve">rookie._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="9">
@@ -512,7 +512,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.earnest[1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest._default[1]</t>
+          <t xml:space="preserve">rookie._default.earnest[1]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="10">
@@ -544,7 +544,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.emotional._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie._default.emotional[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.emotional._default[1]</t>
+          <t xml:space="preserve">rookie._default.emotional[1]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="10">
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.normal[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal._default[1]</t>
+          <t xml:space="preserve">bestMatch._default.normal[1]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="5">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.normal[2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal._default[2]</t>
+          <t xml:space="preserve">bestMatch._default.normal[2]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="5">
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.bold[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold._default[1]</t>
+          <t xml:space="preserve">bestMatch._default.bold[1]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="6">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.bold[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold._default[2]</t>
+          <t xml:space="preserve">bestMatch._default.bold[2]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="6">
@@ -704,7 +704,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.quiet[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.quiet._default[1]</t>
+          <t xml:space="preserve">bestMatch._default.quiet[1]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="7">
@@ -736,7 +736,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.shy._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.shy[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.shy._default[1]</t>
+          <t xml:space="preserve">bestMatch._default.shy[1]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="8">
@@ -768,7 +768,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing._default[1]</t>
+          <t xml:space="preserve">bestMatch._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="9">
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing._default[2]</t>
+          <t xml:space="preserve">bestMatch._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="9">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.earnest[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest._default[1]</t>
+          <t xml:space="preserve">bestMatch._default.earnest[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="10">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.earnest[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest._default[2]</t>
+          <t xml:space="preserve">bestMatch._default.earnest[2]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="10">
@@ -896,7 +896,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.emotional._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch._default.emotional[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.emotional._default[1]</t>
+          <t xml:space="preserve">bestMatch._default.emotional[1]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="10">
@@ -928,7 +928,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.normal[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal._default[1]</t>
+          <t xml:space="preserve">mvp._default.normal[1]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="5">
@@ -960,7 +960,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.normal[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal._default[2]</t>
+          <t xml:space="preserve">mvp._default.normal[2]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="5">
@@ -992,7 +992,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.bold[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold._default[1]</t>
+          <t xml:space="preserve">mvp._default.bold[1]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="6">
@@ -1024,7 +1024,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.bold[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold._default[2]</t>
+          <t xml:space="preserve">mvp._default.bold[2]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="6">
@@ -1056,7 +1056,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.quiet._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.quiet[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.quiet._default[1]</t>
+          <t xml:space="preserve">mvp._default.quiet[1]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="7">
@@ -1088,7 +1088,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.shy._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.shy[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.shy._default[1]</t>
+          <t xml:space="preserve">mvp._default.shy[1]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="8">
@@ -1120,7 +1120,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing._default[1]</t>
+          <t xml:space="preserve">mvp._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="9">
@@ -1152,7 +1152,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing._default[2]</t>
+          <t xml:space="preserve">mvp._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="9">
@@ -1184,7 +1184,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.earnest[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest._default[1]</t>
+          <t xml:space="preserve">mvp._default.earnest[1]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="10">
@@ -1216,7 +1216,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.earnest[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest._default[2]</t>
+          <t xml:space="preserve">mvp._default.earnest[2]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="10">
@@ -1248,7 +1248,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.emotional._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp._default.emotional[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.emotional._default[1]</t>
+          <t xml:space="preserve">mvp._default.emotional[1]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="10">
@@ -1280,7 +1280,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.normal[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal._default[1]</t>
+          <t xml:space="preserve">mediaAward._default.normal[1]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="5">
@@ -1312,7 +1312,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.normal[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal._default[2]</t>
+          <t xml:space="preserve">mediaAward._default.normal[2]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="5">
@@ -1344,7 +1344,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.bold._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.bold[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.bold._default[1]</t>
+          <t xml:space="preserve">mediaAward._default.bold[1]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="6">
@@ -1376,7 +1376,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.bold._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.bold[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.bold._default[2]</t>
+          <t xml:space="preserve">mediaAward._default.bold[2]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="6">
@@ -1408,7 +1408,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.shy._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.shy[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.shy._default[1]</t>
+          <t xml:space="preserve">mediaAward._default.shy[1]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="8">
@@ -1440,7 +1440,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.shy._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.shy[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.shy._default[2]</t>
+          <t xml:space="preserve">mediaAward._default.shy[2]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="8">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.easygoing._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.easygoing._default[1]</t>
+          <t xml:space="preserve">mediaAward._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="9">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.easygoing._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.easygoing._default[2]</t>
+          <t xml:space="preserve">mediaAward._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="9">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.quiet._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward._default.quiet[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.quiet._default[1]</t>
+          <t xml:space="preserve">mediaAward._default.quiet[1]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="7">
@@ -1568,7 +1568,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.normal[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal._default[1]</t>
+          <t xml:space="preserve">champion._default.normal[1]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="5">
@@ -1600,7 +1600,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.normal[2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal._default[2]</t>
+          <t xml:space="preserve">champion._default.normal[2]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="5">
@@ -1632,7 +1632,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.bold[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold._default[1]</t>
+          <t xml:space="preserve">champion._default.bold[1]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="6">
@@ -1664,7 +1664,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.bold[2]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold._default[2]</t>
+          <t xml:space="preserve">champion._default.bold[2]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="6">
@@ -1696,7 +1696,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.quiet._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.quiet[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet._default[1]</t>
+          <t xml:space="preserve">champion._default.quiet[1]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="7">
@@ -1728,7 +1728,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.shy._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.shy[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy._default[1]</t>
+          <t xml:space="preserve">champion._default.shy[1]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="8">
@@ -1760,7 +1760,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing._default[1]</t>
+          <t xml:space="preserve">champion._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="9">
@@ -1792,7 +1792,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.earnest[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest._default[1]</t>
+          <t xml:space="preserve">champion._default.earnest[1]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="10">
@@ -1824,7 +1824,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.earnest[2]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest._default[2]</t>
+          <t xml:space="preserve">champion._default.earnest[2]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="10">
@@ -1856,7 +1856,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.emotional._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion._default.emotional[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional._default[1]</t>
+          <t xml:space="preserve">champion._default.emotional[1]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="10">
@@ -1888,7 +1888,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.normal[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal._default[1]</t>
+          <t xml:space="preserve">hallOfFame._default.normal[1]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="5">
@@ -1920,7 +1920,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.normal[2]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal._default[2]</t>
+          <t xml:space="preserve">hallOfFame._default.normal[2]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="5">
@@ -1952,7 +1952,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.bold[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold._default[1]</t>
+          <t xml:space="preserve">hallOfFame._default.bold[1]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="6">
@@ -1984,7 +1984,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.bold[2]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold._default[2]</t>
+          <t xml:space="preserve">hallOfFame._default.bold[2]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="6">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.quiet[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.quiet._default[1]</t>
+          <t xml:space="preserve">hallOfFame._default.quiet[1]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="7">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.shy._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.shy[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.shy._default[1]</t>
+          <t xml:space="preserve">hallOfFame._default.shy[1]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="8">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing._default[1]</t>
+          <t xml:space="preserve">hallOfFame._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="9">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing._default[2]</t>
+          <t xml:space="preserve">hallOfFame._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="9">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.earnest[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest._default[1]</t>
+          <t xml:space="preserve">hallOfFame._default.earnest[1]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="10">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest._default[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.earnest[2]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest._default[2]</t>
+          <t xml:space="preserve">hallOfFame._default.earnest[2]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="10">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.emotional._default[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame._default.emotional[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.emotional._default[1]</t>
+          <t xml:space="preserve">hallOfFame._default.emotional[1]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="10">
@@ -3757,7 +3757,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal._default[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="5">
@@ -3789,7 +3789,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal._default[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="5">
@@ -3821,7 +3821,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal._default[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
+          <t xml:space="preserve">_default.normal[3]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="5">
@@ -3853,7 +3853,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold._default[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="6">
@@ -3885,7 +3885,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold._default[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="6">
@@ -3917,7 +3917,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold._default[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.bold[3]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[3]</t>
+          <t xml:space="preserve">_default.bold[3]</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="6">
@@ -3949,7 +3949,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="7">
@@ -3981,7 +3981,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="7">
@@ -4013,7 +4013,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet._default[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.quiet[3]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[3]</t>
+          <t xml:space="preserve">_default.quiet[3]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="7">
@@ -4045,7 +4045,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="9">
@@ -4077,7 +4077,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="9">
@@ -4109,7 +4109,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing._default[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[3]</t>
+          <t xml:space="preserve">_default.easygoing[3]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="9">
@@ -4141,7 +4141,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="10">
@@ -4173,7 +4173,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="10">
@@ -4205,7 +4205,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest._default[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.earnest[3]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[3]</t>
+          <t xml:space="preserve">_default.earnest[3]</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="10">
@@ -4237,7 +4237,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="10">
@@ -4269,7 +4269,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="10">
@@ -4301,7 +4301,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional._default[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.emotional[3]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[3]</t>
+          <t xml:space="preserve">_default.emotional[3]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="10">
@@ -4333,7 +4333,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy._default[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="8">
@@ -4365,7 +4365,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy._default[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[2]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="8">
@@ -4397,7 +4397,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy._default[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES._default.shy[3]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[3]</t>
+          <t xml:space="preserve">_default.shy[3]</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="8">
@@ -4429,7 +4429,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal._default[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="5">
@@ -4461,7 +4461,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal._default[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="5">
@@ -4493,7 +4493,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal._default[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
+          <t xml:space="preserve">_default.normal[3]</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="5">
@@ -4525,7 +4525,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold._default[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="6">
@@ -4557,7 +4557,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold._default[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="6">
@@ -4589,7 +4589,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold._default[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.bold[3]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[3]</t>
+          <t xml:space="preserve">_default.bold[3]</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="6">
@@ -4621,7 +4621,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="7">
@@ -4653,7 +4653,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="7">
@@ -4685,7 +4685,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet._default[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.quiet[3]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[3]</t>
+          <t xml:space="preserve">_default.quiet[3]</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="7">
@@ -4717,7 +4717,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="9">
@@ -4749,7 +4749,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="9">
@@ -4781,7 +4781,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing._default[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[3]</t>
+          <t xml:space="preserve">_default.easygoing[3]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="9">
@@ -4813,7 +4813,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="10">
@@ -4845,7 +4845,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="10">
@@ -4877,7 +4877,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest._default[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.earnest[3]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[3]</t>
+          <t xml:space="preserve">_default.earnest[3]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="10">
@@ -4909,7 +4909,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="10">
@@ -4941,7 +4941,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="10">
@@ -4973,7 +4973,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional._default[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.emotional[3]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[3]</t>
+          <t xml:space="preserve">_default.emotional[3]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="10">
@@ -5005,7 +5005,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy._default[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="8">
@@ -5037,7 +5037,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy._default[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[2]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="8">
@@ -5069,7 +5069,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy._default[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES._default.shy[3]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[3]</t>
+          <t xml:space="preserve">_default.shy[3]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="8">

--- a/セリフ編集/ナレーション・記事/称号・記録・年代記.xlsx
+++ b/セリフ編集/ナレーション・記事/称号・記録・年代記.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J343"/>
+  <dimension ref="A1:J341"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="H181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">10代から即戦力。20歳で完成するが、伸びしろは少ない</t>
+          <t xml:space="preserve">10代から即戦力。若いうちに仕上がる成長タイプ</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.遅咲き.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.努力家.en</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6111,19 +6111,19 @@
       </c>
       <c r="E184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">遅咲き.en</t>
+          <t xml:space="preserve">努力家.en</t>
         </is>
       </c>
       <c r="H184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Late Starter</t>
+          <t xml:space="preserve">Hard Worker</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.遅咲き.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.努力家.desc</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6143,19 +6143,19 @@
       </c>
       <c r="E185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">遅咲き.desc</t>
+          <t xml:space="preserve">努力家.desc</t>
         </is>
       </c>
       <c r="H185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">序盤は全く伸びないが、23歳で突然覚醒する</t>
+          <t xml:space="preserve">成長が安定しやすく、練習で体を壊しにくい</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.努力家.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.破天荒.desc</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6175,19 +6175,19 @@
       </c>
       <c r="E186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">努力家.en</t>
+          <t xml:space="preserve">破天荒.desc</t>
         </is>
       </c>
       <c r="H186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Hard Worker</t>
+          <t xml:space="preserve">成長にムラあり。爆発的か停滞</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.努力家.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.適応力.desc</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6207,19 +6207,19 @@
       </c>
       <c r="E187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">努力家.desc</t>
+          <t xml:space="preserve">適応力.desc</t>
         </is>
       </c>
       <c r="H187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">成長が安定しやすく、練習で体を壊しにくい</t>
+          <t xml:space="preserve">怪我中でも成長が落ちにくく、追い込み練習にも強い</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.破天荒.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.頑丈さ.desc</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6239,19 +6239,19 @@
       </c>
       <c r="E188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">破天荒.desc</t>
+          <t xml:space="preserve">頑丈さ.desc</t>
         </is>
       </c>
       <c r="H188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">成長にムラあり。爆発的か停滞</t>
+          <t xml:space="preserve">怪我しにくい</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.適応力.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.ガラスの身体.en</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6271,19 +6271,19 @@
       </c>
       <c r="E189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">適応力.desc</t>
+          <t xml:space="preserve">ガラスの身体.en</t>
         </is>
       </c>
       <c r="H189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我中でも成長が落ちにくく、追い込み練習にも強い</t>
+          <t xml:space="preserve">Glass Body</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.頑丈さ.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.ガラスの身体.desc</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6303,19 +6303,19 @@
       </c>
       <c r="E190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">頑丈さ.desc</t>
+          <t xml:space="preserve">ガラスの身体.desc</t>
         </is>
       </c>
       <c r="H190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我しにくい</t>
+          <t xml:space="preserve">怪我しやすいが、復帰のたびにファンの声援を集める</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ガラスの身体.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.鉄人.en</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6335,19 +6335,19 @@
       </c>
       <c r="E191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ガラスの身体.en</t>
+          <t xml:space="preserve">鉄人.en</t>
         </is>
       </c>
       <c r="H191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Glass Body</t>
+          <t xml:space="preserve">Iron Man</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ガラスの身体.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.鉄人.desc</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6367,19 +6367,19 @@
       </c>
       <c r="E192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ガラスの身体.desc</t>
+          <t xml:space="preserve">鉄人.desc</t>
         </is>
       </c>
       <c r="H192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我しやすいが、復帰のたびにファンの声援を集める</t>
+          <t xml:space="preserve">コンディション全般に強い</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.鉄人.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.不屈.desc</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6399,19 +6399,19 @@
       </c>
       <c r="E193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">鉄人.en</t>
+          <t xml:space="preserve">不屈.desc</t>
         </is>
       </c>
       <c r="H193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Iron Man</t>
+          <t xml:space="preserve">怪我からの復帰が速い</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.鉄人.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.ムードメーカー.en</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6431,19 +6431,19 @@
       </c>
       <c r="E194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">鉄人.desc</t>
+          <t xml:space="preserve">ムードメーカー.en</t>
         </is>
       </c>
       <c r="H194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コンディション全般に強い</t>
+          <t xml:space="preserve">Mood Maker</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.不屈.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.ムードメーカー.desc</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6463,19 +6463,19 @@
       </c>
       <c r="E195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">不屈.desc</t>
+          <t xml:space="preserve">ムードメーカー.desc</t>
         </is>
       </c>
       <c r="H195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我からの復帰が速い</t>
+          <t xml:space="preserve">明るさでロッカールームの空気を持ち上げる（雰囲気が良い時は効果が薄れる）</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ムードメーカー.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.人望.desc</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6495,19 +6495,19 @@
       </c>
       <c r="E196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ムードメーカー.en</t>
+          <t xml:space="preserve">人望.desc</t>
         </is>
       </c>
       <c r="H196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Mood Maker</t>
+          <t xml:space="preserve">不安定な選手たちの心を支える（不満が多い時ほど効果が大きい）</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.ムードメーカー.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.負けず嫌い.desc</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6527,19 +6527,19 @@
       </c>
       <c r="E197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ムードメーカー.desc</t>
+          <t xml:space="preserve">負けず嫌い.desc</t>
         </is>
       </c>
       <c r="H197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">明るさでロッカールームの空気を持ち上げる（雰囲気が良い時は効果が薄れる）</t>
+          <t xml:space="preserve">負けた翌週の練習成長にボーナス</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.人望.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.リーダー気質.desc</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6559,19 +6559,19 @@
       </c>
       <c r="E198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">人望.desc</t>
+          <t xml:space="preserve">リーダー気質.desc</t>
         </is>
       </c>
       <c r="H198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不安定な選手たちの心を支える（不満が多い時ほど効果が大きい）</t>
+          <t xml:space="preserve">チームの不満を抑え、チャンピオン時は団体の顔として人気UP</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.負けず嫌い.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.忠誠心.desc</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6591,19 +6591,19 @@
       </c>
       <c r="E199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">負けず嫌い.desc</t>
+          <t xml:space="preserve">忠誠心.desc</t>
         </is>
       </c>
       <c r="H199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた翌週の練習成長にボーナス</t>
+          <t xml:space="preserve">引き抜きオファーが来る確率が大幅に低下</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.リーダー気質.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.野心.desc</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6623,19 +6623,19 @@
       </c>
       <c r="E200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">リーダー気質.desc</t>
+          <t xml:space="preserve">野心.desc</t>
         </is>
       </c>
       <c r="H200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チームの不満を抑え、チャンピオン時は団体の顔として人気UP</t>
+          <t xml:space="preserve">タイトル挑戦時に試合が盛り上がり、覚醒しやすい</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.忠誠心.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.番狂わせ体質.en</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6655,19 +6655,19 @@
       </c>
       <c r="E201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">忠誠心.desc</t>
+          <t xml:space="preserve">番狂わせ体質.en</t>
         </is>
       </c>
       <c r="H201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き抜きオファーが来る確率が大幅に低下</t>
+          <t xml:space="preserve">Upset Specialist</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.野心.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.番狂わせ体質.desc</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6687,19 +6687,19 @@
       </c>
       <c r="E202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">野心.desc</t>
+          <t xml:space="preserve">番狂わせ体質.desc</t>
         </is>
       </c>
       <c r="H202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトル挑戦時に試合が盛り上がり、覚醒しやすい</t>
+          <t xml:space="preserve">格上相手に丸め込み率UP</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.番狂わせ体質.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.闘志.en</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6719,19 +6719,19 @@
       </c>
       <c r="E203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">番狂わせ体質.en</t>
+          <t xml:space="preserve">闘志.en</t>
         </is>
       </c>
       <c r="H203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Upset Specialist</t>
+          <t xml:space="preserve">Fighting Spirit</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.番狂わせ体質.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.闘志.desc</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="E204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">番狂わせ体質.desc</t>
+          <t xml:space="preserve">闘志.desc</t>
         </is>
       </c>
       <c r="H204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格上相手に丸め込み率UP</t>
+          <t xml:space="preserve">瀕死から粘る力が強く、負けても人気が落ちにくい</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.闘志.en</t>
+          <t xml:space="preserve">TRAIT_DEFS.威圧感.desc</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6783,19 +6783,19 @@
       </c>
       <c r="E205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">闘志.en</t>
+          <t xml:space="preserve">威圧感.desc</t>
         </is>
       </c>
       <c r="H205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Fighting Spirit</t>
+          <t xml:space="preserve">対戦相手の序盤モメンタムが不利</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.闘志.desc</t>
+          <t xml:space="preserve">TRAIT_DEFS.反骨心.desc</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6815,19 +6815,19 @@
       </c>
       <c r="E206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">闘志.desc</t>
+          <t xml:space="preserve">反骨心.desc</t>
         </is>
       </c>
       <c r="H206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">瀕死から粘る力が強く、負けても人気が落ちにくい</t>
+          <t xml:space="preserve">移籍願望が出やすいが、信頼が低いと成長する</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.威圧感.desc</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.striker</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6837,29 +6837,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">威圧感.desc</t>
+          <t xml:space="preserve">striker</t>
         </is>
       </c>
       <c r="H207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対戦相手の序盤モメンタムが不利</t>
+          <t xml:space="preserve">打撃</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS.反骨心.desc</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.grappler</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6869,29 +6869,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAIT_DEFS</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">反骨心.desc</t>
+          <t xml:space="preserve">grappler</t>
         </is>
       </c>
       <c r="H208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">移籍願望が出やすいが、信頼が低いと成長する</t>
+          <t xml:space="preserve">組技</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.striker</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.submission</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6911,19 +6911,19 @@
       </c>
       <c r="E209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">striker</t>
+          <t xml:space="preserve">submission</t>
         </is>
       </c>
       <c r="H209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打撃</t>
+          <t xml:space="preserve">関節技</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.grappler</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.brawler</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6943,19 +6943,19 @@
       </c>
       <c r="E210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">grappler</t>
+          <t xml:space="preserve">brawler</t>
         </is>
       </c>
       <c r="H210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">組技</t>
+          <t xml:space="preserve">喧嘩</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.submission</t>
+          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.allround</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6975,19 +6975,19 @@
       </c>
       <c r="E211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">submission</t>
+          <t xml:space="preserve">allround</t>
         </is>
       </c>
       <c r="H211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関節技</t>
+          <t xml:space="preserve">万能</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.brawler</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7002,24 +7002,24 @@
       </c>
       <c r="D212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">brawler</t>
+          <t xml:space="preserve">early[1]</t>
         </is>
       </c>
       <c r="H212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">喧嘩</t>
+          <t xml:space="preserve">旗揚げ世代</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS.allround</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7034,24 +7034,24 @@
       </c>
       <c r="D213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.AXIS_LABELS</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">allround</t>
+          <t xml:space="preserve">early[2]</t>
         </is>
       </c>
       <c r="H213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">万能</t>
+          <t xml:space="preserve">創成期</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[3]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7071,19 +7071,19 @@
       </c>
       <c r="E214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">early[1]</t>
+          <t xml:space="preserve">early[3]</t>
         </is>
       </c>
       <c r="H214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">旗揚げ世代</t>
+          <t xml:space="preserve">始まりの灯</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[4]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7103,19 +7103,19 @@
       </c>
       <c r="E215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">early[2]</t>
+          <t xml:space="preserve">early[4]</t>
         </is>
       </c>
       <c r="H215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">創成期</t>
+          <t xml:space="preserve">旗を立てた日々</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7135,19 +7135,19 @@
       </c>
       <c r="E216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">early[3]</t>
+          <t xml:space="preserve">golden[1]</t>
         </is>
       </c>
       <c r="H216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">始まりの灯</t>
+          <t xml:space="preserve">黄金期</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.early[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7167,19 +7167,19 @@
       </c>
       <c r="E217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">early[4]</t>
+          <t xml:space="preserve">golden[2]</t>
         </is>
       </c>
       <c r="H217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">旗を立てた日々</t>
+          <t xml:space="preserve">一強時代</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[3]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7199,19 +7199,19 @@
       </c>
       <c r="E218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">golden[1]</t>
+          <t xml:space="preserve">golden[3]</t>
         </is>
       </c>
       <c r="H218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黄金期</t>
+          <t xml:space="preserve">連続王者の時代</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[4]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7231,19 +7231,19 @@
       </c>
       <c r="E219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">golden[2]</t>
+          <t xml:space="preserve">golden[4]</t>
         </is>
       </c>
       <c r="H219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一強時代</t>
+          <t xml:space="preserve">誰にも届かぬ高み</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7263,19 +7263,19 @@
       </c>
       <c r="E220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">golden[3]</t>
+          <t xml:space="preserve">almostThere[1]</t>
         </is>
       </c>
       <c r="H220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連続王者の時代</t>
+          <t xml:space="preserve">届かなかった頂</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.golden[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7295,19 +7295,19 @@
       </c>
       <c r="E221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">golden[4]</t>
+          <t xml:space="preserve">almostThere[2]</t>
         </is>
       </c>
       <c r="H221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰にも届かぬ高み</t>
+          <t xml:space="preserve">壁の前で</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[3]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7327,19 +7327,19 @@
       </c>
       <c r="E222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[1]</t>
+          <t xml:space="preserve">almostThere[3]</t>
         </is>
       </c>
       <c r="H222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">届かなかった頂</t>
+          <t xml:space="preserve">頂を仰ぐ者たち</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[4]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7359,19 +7359,19 @@
       </c>
       <c r="E223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[2]</t>
+          <t xml:space="preserve">almostThere[4]</t>
         </is>
       </c>
       <c r="H223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁の前で</t>
+          <t xml:space="preserve">一歩、届かず</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[5]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7391,19 +7391,19 @@
       </c>
       <c r="E224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[3]</t>
+          <t xml:space="preserve">almostThere[5]</t>
         </is>
       </c>
       <c r="H224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂を仰ぐ者たち</t>
+          <t xml:space="preserve">影を踏んだ世代</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7423,19 +7423,19 @@
       </c>
       <c r="E225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[4]</t>
+          <t xml:space="preserve">challenge[1]</t>
         </is>
       </c>
       <c r="H225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一歩、届かず</t>
+          <t xml:space="preserve">挑戦者世代</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.almostThere[5]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7455,19 +7455,19 @@
       </c>
       <c r="E226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">almostThere[5]</t>
+          <t xml:space="preserve">challenge[2]</t>
         </is>
       </c>
       <c r="H226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">影を踏んだ世代</t>
+          <t xml:space="preserve">気鋭の時代</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[3]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7487,19 +7487,19 @@
       </c>
       <c r="E227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">challenge[1]</t>
+          <t xml:space="preserve">challenge[3]</t>
         </is>
       </c>
       <c r="H227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑戦者世代</t>
+          <t xml:space="preserve">牙を研ぐ日々</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[4]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7519,19 +7519,19 @@
       </c>
       <c r="E228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">challenge[2]</t>
+          <t xml:space="preserve">challenge[4]</t>
         </is>
       </c>
       <c r="H228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気鋭の時代</t>
+          <t xml:space="preserve">壁にぶつかった世代</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7551,19 +7551,19 @@
       </c>
       <c r="E229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">challenge[3]</t>
+          <t xml:space="preserve">idol[1]</t>
         </is>
       </c>
       <c r="H229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">牙を研ぐ日々</t>
+          <t xml:space="preserve">華やかなる時代</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.challenge[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7583,19 +7583,19 @@
       </c>
       <c r="E230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">challenge[4]</t>
+          <t xml:space="preserve">idol[2]</t>
         </is>
       </c>
       <c r="H230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁にぶつかった世代</t>
+          <t xml:space="preserve">熱気と歓声の時代</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[3]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7615,19 +7615,19 @@
       </c>
       <c r="E231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">idol[1]</t>
+          <t xml:space="preserve">idol[3]</t>
         </is>
       </c>
       <c r="H231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">華やかなる時代</t>
+          <t xml:space="preserve">ファン人気で支えた世代</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[4]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7647,19 +7647,19 @@
       </c>
       <c r="E232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">idol[2]</t>
+          <t xml:space="preserve">idol[4]</t>
         </is>
       </c>
       <c r="H232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱気と歓声の時代</t>
+          <t xml:space="preserve">華のある世代</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7679,19 +7679,19 @@
       </c>
       <c r="E233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">idol[3]</t>
+          <t xml:space="preserve">enduring[1]</t>
         </is>
       </c>
       <c r="H233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファン人気で支えた世代</t>
+          <t xml:space="preserve">低迷期</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.idol[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7711,19 +7711,19 @@
       </c>
       <c r="E234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">idol[4]</t>
+          <t xml:space="preserve">enduring[2]</t>
         </is>
       </c>
       <c r="H234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">華のある世代</t>
+          <t xml:space="preserve">日陰の奉仕者たち</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[3]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7743,19 +7743,19 @@
       </c>
       <c r="E235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enduring[1]</t>
+          <t xml:space="preserve">enduring[3]</t>
         </is>
       </c>
       <c r="H235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">低迷期</t>
+          <t xml:space="preserve">灯を絶やさぬ者たち</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[4]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7775,19 +7775,19 @@
       </c>
       <c r="E236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enduring[2]</t>
+          <t xml:space="preserve">enduring[4]</t>
         </is>
       </c>
       <c r="H236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日陰の奉仕者たち</t>
+          <t xml:space="preserve">世代交代期</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[3]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7807,19 +7807,19 @@
       </c>
       <c r="E237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enduring[3]</t>
+          <t xml:space="preserve">other[1]</t>
         </is>
       </c>
       <c r="H237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">灯を絶やさぬ者たち</t>
+          <t xml:space="preserve">中堅職人世代</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.enduring[4]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7839,19 +7839,19 @@
       </c>
       <c r="E238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enduring[4]</t>
+          <t xml:space="preserve">other[2]</t>
         </is>
       </c>
       <c r="H238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世代交代期</t>
+          <t xml:space="preserve">残留組の時代</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[1]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[3]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7871,19 +7871,19 @@
       </c>
       <c r="E239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">other[1]</t>
+          <t xml:space="preserve">other[3]</t>
         </is>
       </c>
       <c r="H239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">中堅職人世代</t>
+          <t xml:space="preserve">端境期</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[2]</t>
+          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[4]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7903,19 +7903,19 @@
       </c>
       <c r="E240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">other[2]</t>
+          <t xml:space="preserve">other[4]</t>
         </is>
       </c>
       <c r="H240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残留組の時代</t>
+          <t xml:space="preserve">過渡期世代</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[3]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7930,24 +7930,24 @@
       </c>
       <c r="D241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">other[3]</t>
+          <t xml:space="preserve">slight[1]</t>
         </is>
       </c>
       <c r="H241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">端境期</t>
+          <t xml:space="preserve">この世代は、{org}のスタイルを少しだけ{axis}寄りにした。</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES.other[4]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7962,24 +7962,24 @@
       </c>
       <c r="D242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.SUBTITLE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">other[4]</t>
+          <t xml:space="preserve">slight[2]</t>
         </is>
       </c>
       <c r="H242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">過渡期世代</t>
+          <t xml:space="preserve">{org}の試合内容に{axis}の傾向が少し混じり始めた。</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[1]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[3]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -7999,19 +7999,19 @@
       </c>
       <c r="E243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">slight[1]</t>
+          <t xml:space="preserve">slight[3]</t>
         </is>
       </c>
       <c r="H243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代は、{org}のスタイルを少しだけ{axis}寄りにした。</t>
+          <t xml:space="preserve">この世代は{org}に{axis}の傾向をわずかに残した。</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[2]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[4]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8031,19 +8031,19 @@
       </c>
       <c r="E244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">slight[2]</t>
+          <t xml:space="preserve">slight[4]</t>
         </is>
       </c>
       <c r="H244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{org}の試合内容に{axis}の傾向が少し混じり始めた。</t>
+          <t xml:space="preserve">{org}の基本路線に{axis}の要素が少し加わった。</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[3]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8063,19 +8063,19 @@
       </c>
       <c r="E245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">slight[3]</t>
+          <t xml:space="preserve">moderate[1]</t>
         </is>
       </c>
       <c r="H245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代は{org}に{axis}の傾向をわずかに残した。</t>
+          <t xml:space="preserve">この世代は{org}のスタイルに{axis}色を残した。</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.slight[4]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8095,19 +8095,19 @@
       </c>
       <c r="E246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">slight[4]</t>
+          <t xml:space="preserve">moderate[2]</t>
         </is>
       </c>
       <c r="H246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{org}の基本路線に{axis}の要素が少し加わった。</t>
+          <t xml:space="preserve">{axis}中心の試合運びが、{org}全体の傾向を少し変えた。</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[1]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[3]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8127,19 +8127,19 @@
       </c>
       <c r="E247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[1]</t>
+          <t xml:space="preserve">moderate[3]</t>
         </is>
       </c>
       <c r="H247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代は{org}のスタイルに{axis}色を残した。</t>
+          <t xml:space="preserve">次世代の選手は{axis}を一つの基準として育っていった。</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[2]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[4]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8159,19 +8159,19 @@
       </c>
       <c r="E248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[2]</t>
+          <t xml:space="preserve">moderate[4]</t>
         </is>
       </c>
       <c r="H248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{axis}中心の試合運びが、{org}全体の傾向を少し変えた。</t>
+          <t xml:space="preserve">{org}が{axis}を団体の特色として語れるようになったのは、この世代からだった。</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[3]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8191,19 +8191,19 @@
       </c>
       <c r="E249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[3]</t>
+          <t xml:space="preserve">strong[1]</t>
         </is>
       </c>
       <c r="H249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次世代の選手は{axis}を一つの基準として育っていった。</t>
+          <t xml:space="preserve">この世代を経て、{org}のスタイルは{axis}色が明確になった。</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.moderate[4]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8223,19 +8223,19 @@
       </c>
       <c r="E250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[4]</t>
+          <t xml:space="preserve">strong[2]</t>
         </is>
       </c>
       <c r="H250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{org}が{axis}を団体の特色として語れるようになったのは、この世代からだった。</t>
+          <t xml:space="preserve">この世代以降、{org}の若手は{axis}を基本として選ぶようになった。</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[1]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[3]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8255,19 +8255,19 @@
       </c>
       <c r="E251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">strong[1]</t>
+          <t xml:space="preserve">strong[3]</t>
         </is>
       </c>
       <c r="H251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代を経て、{org}のスタイルは{axis}色が明確になった。</t>
+          <t xml:space="preserve">{axis}が{org}の代名詞として定着した時期だった。</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[2]</t>
+          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[4]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8287,19 +8287,19 @@
       </c>
       <c r="E252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">strong[2]</t>
+          <t xml:space="preserve">strong[4]</t>
         </is>
       </c>
       <c r="H252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代以降、{org}の若手は{axis}を基本として選ぶようになった。</t>
+          <t xml:space="preserve">この世代以降、{org}の主流は{axis}に移った。</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8314,24 +8314,24 @@
       </c>
       <c r="D253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">strong[3]</t>
+          <t xml:space="preserve">peakDefender[1]</t>
         </is>
       </c>
       <c r="H253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{axis}が{org}の代名詞として定着した時期だった。</t>
+          <t xml:space="preserve">{surname}は章を通じて{defenses}度の防衛を積み上げ、団体の中心軸であり続けた。</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES.strong[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8346,24 +8346,24 @@
       </c>
       <c r="D254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.CLOSING_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">strong[4]</t>
+          <t xml:space="preserve">peakDefender[2]</t>
         </is>
       </c>
       <c r="H254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この世代以降、{org}の主流は{axis}に移った。</t>
+          <t xml:space="preserve">挑戦者を{defenses}度退けた{surname}は、この章の屋台骨だった。</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[3]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8383,19 +8383,19 @@
       </c>
       <c r="E255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender[1]</t>
+          <t xml:space="preserve">peakDefender[3]</t>
         </is>
       </c>
       <c r="H255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は章を通じて{defenses}度の防衛を積み上げ、団体の中心軸であり続けた。</t>
+          <t xml:space="preserve">{defenses}度防衛——{surname}が王座にいる時間が、この世代の輪郭を形作った。</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[4]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8415,19 +8415,19 @@
       </c>
       <c r="E256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender[2]</t>
+          <t xml:space="preserve">peakDefender[4]</t>
         </is>
       </c>
       <c r="H256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑戦者を{defenses}度退けた{surname}は、この章の屋台骨だった。</t>
+          <t xml:space="preserve">{defenses}度の防衛を重ねた{surname}は、団体の絶対的な軸として君臨した。</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8447,19 +8447,19 @@
       </c>
       <c r="E257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender[3]</t>
+          <t xml:space="preserve">defender[1]</t>
         </is>
       </c>
       <c r="H257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{defenses}度防衛——{surname}が王座にいる時間が、この世代の輪郭を形作った。</t>
+          <t xml:space="preserve">{surname}は王座を{defenses}度防衛し、団体の核として時代を背負った。</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.peakDefender[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="E258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender[4]</t>
+          <t xml:space="preserve">defender[2]</t>
         </is>
       </c>
       <c r="H258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{defenses}度の防衛を重ねた{surname}は、団体の絶対的な軸として君臨した。</t>
+          <t xml:space="preserve">{titleReigns}度の戴冠と{defenses}度の防衛。{surname}が立っていることが、団体の安定そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[3]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8511,19 +8511,19 @@
       </c>
       <c r="E259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender[1]</t>
+          <t xml:space="preserve">defender[3]</t>
         </is>
       </c>
       <c r="H259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は王座を{defenses}度防衛し、団体の核として時代を背負った。</t>
+          <t xml:space="preserve">{surname}は王座を離さなかった。挑戦者たちはなかなか手が届かなかった。</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[4]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8543,19 +8543,19 @@
       </c>
       <c r="E260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender[2]</t>
+          <t xml:space="preserve">defender[4]</t>
         </is>
       </c>
       <c r="H260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{titleReigns}度の戴冠と{defenses}度の防衛。{surname}が立っていることが、団体の安定そのものだった。</t>
+          <t xml:space="preserve">{surname}の{defenses}度の防衛は、この章の屋台骨だった。</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8575,19 +8575,19 @@
       </c>
       <c r="E261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender[3]</t>
+          <t xml:space="preserve">champion[1]</t>
         </is>
       </c>
       <c r="H261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は王座を離さなかった。挑戦者たちはなかなか手が届かなかった。</t>
+          <t xml:space="preserve">{surname}は{titleReigns}度の戴冠を経て、この章の主役を担った。</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.defender[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8607,19 +8607,19 @@
       </c>
       <c r="E262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender[4]</t>
+          <t xml:space="preserve">champion[2]</t>
         </is>
       </c>
       <c r="H262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の{defenses}度の防衛は、この章の屋台骨だった。</t>
+          <t xml:space="preserve">{titleReigns}度の戴冠を重ねた{surname}は、この世代の中心人物の一人だった。</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[3]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8639,19 +8639,19 @@
       </c>
       <c r="E263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion[1]</t>
+          <t xml:space="preserve">champion[3]</t>
         </is>
       </c>
       <c r="H263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{titleReigns}度の戴冠を経て、この章の主役を担った。</t>
+          <t xml:space="preserve">何度王座から落ちても、{surname}は戻ってきた。{titleReigns}度の戴冠はその粘りの証だった。</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[4]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8671,19 +8671,19 @@
       </c>
       <c r="E264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion[2]</t>
+          <t xml:space="preserve">champion[4]</t>
         </is>
       </c>
       <c r="H264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{titleReigns}度の戴冠を重ねた{surname}は、この世代の中心人物の一人だった。</t>
+          <t xml:space="preserve">{titleReigns}度の戴冠を通じて、{surname}はこの章の流れを作った。</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8703,19 +8703,19 @@
       </c>
       <c r="E265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion[3]</t>
+          <t xml:space="preserve">popStar[1]</t>
         </is>
       </c>
       <c r="H265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度王座から落ちても、{surname}は戻ってきた。{titleReigns}度の戴冠はその粘りの証だった。</t>
+          <t xml:space="preserve">{surname}の人気が客足を支えた。戦績ではなく動員で、時代を作った世代だった。</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.champion[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8735,19 +8735,19 @@
       </c>
       <c r="E266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion[4]</t>
+          <t xml:space="preserve">popStar[2]</t>
         </is>
       </c>
       <c r="H266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{titleReigns}度の戴冠を通じて、{surname}はこの章の流れを作った。</t>
+          <t xml:space="preserve">王座にこそ恵まれなかったが、{surname}の華やかさが客席を埋めた。</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[3]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8767,19 +8767,19 @@
       </c>
       <c r="E267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar[1]</t>
+          <t xml:space="preserve">popStar[3]</t>
         </is>
       </c>
       <c r="H267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の人気が客足を支えた。戦績ではなく動員で、時代を作った世代だった。</t>
+          <t xml:space="preserve">試合記録には残らない記憶というものを、{surname}は、その人気でこの世代に刻みつけた。</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[4]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8799,19 +8799,19 @@
       </c>
       <c r="E268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar[2]</t>
+          <t xml:space="preserve">popStar[4]</t>
         </is>
       </c>
       <c r="H268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座にこそ恵まれなかったが、{surname}の華やかさが客席を埋めた。</t>
+          <t xml:space="preserve">{surname}を見るために客が会場に押し寄せた。それがこの世代の正体だった。</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8831,19 +8831,19 @@
       </c>
       <c r="E269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar[3]</t>
+          <t xml:space="preserve">generationShift[1]</t>
         </is>
       </c>
       <c r="H269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合記録には残らない記憶というものを、{surname}は、その人気でこの世代に刻みつけた。</t>
+          <t xml:space="preserve">{surname}は前世代の主役たちと並走し、世代交代の橋渡しとなった。</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.popStar[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8863,19 +8863,19 @@
       </c>
       <c r="E270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar[4]</t>
+          <t xml:space="preserve">generationShift[2]</t>
         </is>
       </c>
       <c r="H270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}を見るために客が会場に押し寄せた。それがこの世代の正体だった。</t>
+          <t xml:space="preserve">{surname}の章は、過去と未来が混じり合った時間として団体史に残る。</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[3]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8895,19 +8895,19 @@
       </c>
       <c r="E271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift[1]</t>
+          <t xml:space="preserve">generationShift[3]</t>
         </is>
       </c>
       <c r="H271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は前世代の主役たちと並走し、世代交代の橋渡しとなった。</t>
+          <t xml:space="preserve">前章の主役たちが退いていく中、{surname}が次の中心を担った。</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[4]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8927,19 +8927,19 @@
       </c>
       <c r="E272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift[2]</t>
+          <t xml:space="preserve">generationShift[4]</t>
         </is>
       </c>
       <c r="H272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章は、過去と未来が混じり合った時間として団体史に残る。</t>
+          <t xml:space="preserve">{surname}は古参と新参の間に立ち、団体の世代を繋いだ。</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8959,19 +8959,19 @@
       </c>
       <c r="E273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift[3]</t>
+          <t xml:space="preserve">struggle[1]</t>
         </is>
       </c>
       <c r="H273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前章の主役たちが退いていく中、{surname}が次の中心を担った。</t>
+          <t xml:space="preserve">{surname}は{styleJa}を貫いたが、上位の壁は厚かった。届かないまま章は閉じる。</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.generationShift[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8991,19 +8991,19 @@
       </c>
       <c r="E274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift[4]</t>
+          <t xml:space="preserve">struggle[2]</t>
         </is>
       </c>
       <c r="H274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は古参と新参の間に立ち、団体の世代を繋いだ。</t>
+          <t xml:space="preserve">挑んでは敗れ、それでも{surname}は{styleJa}を捨てなかった。届かなかった世代の象徴である。</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[3]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9023,19 +9023,19 @@
       </c>
       <c r="E275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle[1]</t>
+          <t xml:space="preserve">struggle[3]</t>
         </is>
       </c>
       <c r="H275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{styleJa}を貫いたが、上位の壁は厚かった。届かないまま章は閉じる。</t>
+          <t xml:space="preserve">{surname}の章は、勝てなかった日々の記録である。だが、それでも諦めず挑戦を続けた日々の記録でもある。</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[4]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9055,19 +9055,19 @@
       </c>
       <c r="E276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle[2]</t>
+          <t xml:space="preserve">struggle[4]</t>
         </is>
       </c>
       <c r="H276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑んでは敗れ、それでも{surname}は{styleJa}を捨てなかった。届かなかった世代の象徴である。</t>
+          <t xml:space="preserve">{surname}は何度も上位に挑み、何度も敗れた。それでも立ち上がり続けた世代だった。</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9087,19 +9087,19 @@
       </c>
       <c r="E277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle[3]</t>
+          <t xml:space="preserve">craftsman[1]</t>
         </is>
       </c>
       <c r="H277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章は、勝てなかった日々の記録である。だが、それでも諦めず挑戦を続けた日々の記録でもある。</t>
+          <t xml:space="preserve">{surname}は{styleJa}を武器に団体を支えた。王座にこそ届かなかったが、世代の支柱だった。</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.struggle[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9119,19 +9119,19 @@
       </c>
       <c r="E278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle[4]</t>
+          <t xml:space="preserve">craftsman[2]</t>
         </is>
       </c>
       <c r="H278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は何度も上位に挑み、何度も敗れた。それでも立ち上がり続けた世代だった。</t>
+          <t xml:space="preserve">OVR{peakOVR}に達した{surname}は、無冠ながら誰よりも信頼される選手だった。</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[3]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9151,19 +9151,19 @@
       </c>
       <c r="E279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman[1]</t>
+          <t xml:space="preserve">craftsman[3]</t>
         </is>
       </c>
       <c r="H279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{styleJa}を武器に団体を支えた。王座にこそ届かなかったが、世代の支柱だった。</t>
+          <t xml:space="preserve">{surname}の{styleJa}は派手さこそないが、団体を底から支え続けた。</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[4]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9183,19 +9183,19 @@
       </c>
       <c r="E280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman[2]</t>
+          <t xml:space="preserve">craftsman[4]</t>
         </is>
       </c>
       <c r="H280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR{peakOVR}に達した{surname}は、無冠ながら誰よりも信頼される選手だった。</t>
+          <t xml:space="preserve">王座とは縁がなかったが、{surname}の{styleJa}はこの章の地力そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9215,19 +9215,19 @@
       </c>
       <c r="E281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman[3]</t>
+          <t xml:space="preserve">uncrowned[1]</t>
         </is>
       </c>
       <c r="H281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の{styleJa}は派手さこそないが、団体を底から支え続けた。</t>
+          <t xml:space="preserve">{surname}は無冠ながらこの世代の主役だった。タイトルでは測れない存在感がそこにあった。</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.craftsman[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9247,19 +9247,19 @@
       </c>
       <c r="E282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman[4]</t>
+          <t xml:space="preserve">uncrowned[2]</t>
         </is>
       </c>
       <c r="H282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座とは縁がなかったが、{surname}の{styleJa}はこの章の地力そのものだった。</t>
+          <t xml:space="preserve">王座を獲ることはなかったが、{surname}抜きにこの章は語れない。</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[3]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9279,19 +9279,19 @@
       </c>
       <c r="E283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned[1]</t>
+          <t xml:space="preserve">uncrowned[3]</t>
         </is>
       </c>
       <c r="H283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は無冠ながらこの世代の主役だった。タイトルでは測れない存在感がそこにあった。</t>
+          <t xml:space="preserve">{surname}は最後までベルトを巻かなかった。だが団体史はこの選手を主役として記憶する。</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[4]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9311,19 +9311,19 @@
       </c>
       <c r="E284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned[2]</t>
+          <t xml:space="preserve">uncrowned[4]</t>
         </is>
       </c>
       <c r="H284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座を獲ることはなかったが、{surname}抜きにこの章は語れない。</t>
+          <t xml:space="preserve">記録には残らないが、記憶には深く残る。{surname}はそういう世代の主役だった。</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9338,24 +9338,24 @@
       </c>
       <c r="D285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned[3]</t>
+          <t xml:space="preserve">sectionA[1]</t>
         </is>
       </c>
       <c r="H285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は最後までベルトを巻かなかった。だが団体史はこの選手を主役として記憶する。</t>
+          <t xml:space="preserve">{surname1}と{surname2}は二枚看板としてこの章の主役を担った。{topRivalClause}{warClause}</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES.uncrowned[4]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9370,24 +9370,24 @@
       </c>
       <c r="D286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned[4]</t>
+          <t xml:space="preserve">sectionA[2]</t>
         </is>
       </c>
       <c r="H286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">記録には残らないが、記憶には深く残る。{surname}はそういう世代の主役だった。</t>
+          <t xml:space="preserve">{surname1}と{surname2}が並走したこの章は、二人の名前なしには語れない。{topVenueClause}</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[3]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9407,19 +9407,19 @@
       </c>
       <c r="E287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionA[1]</t>
+          <t xml:space="preserve">sectionA[3]</t>
         </is>
       </c>
       <c r="H287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname1}と{surname2}は二枚看板としてこの章の主役を担った。{topRivalClause}{warClause}</t>
+          <t xml:space="preserve">王座とリングの中心を{surname1}と{surname2}が分け合い、団体は二つの頂を持つ時代に入った。</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9439,19 +9439,19 @@
       </c>
       <c r="E288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionA[2]</t>
+          <t xml:space="preserve">sectionB[1]</t>
         </is>
       </c>
       <c r="H288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname1}と{surname2}が並走したこの章は、二人の名前なしには語れない。{topVenueClause}</t>
+          <t xml:space="preserve">二人が引っ張った時代、{org}全体の試合運びには{spiritAxis}の色が濃く染み込んでいった。</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionA[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9471,19 +9471,19 @@
       </c>
       <c r="E289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionA[3]</t>
+          <t xml:space="preserve">sectionB[2]</t>
         </is>
       </c>
       <c r="H289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座とリングの中心を{surname1}と{surname2}が分け合い、団体は二つの頂を持つ時代に入った。</t>
+          <t xml:space="preserve">{eraTag}と呼ばれるこの章で、{surname1}と{surname2}はそれぞれ別の頂点を立てた。</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[3]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9503,19 +9503,19 @@
       </c>
       <c r="E290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionB[1]</t>
+          <t xml:space="preserve">sectionB[3]</t>
         </is>
       </c>
       <c r="H290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人が引っ張った時代、{org}全体の試合運びには{spiritAxis}の色が濃く染み込んでいった。</t>
+          <t xml:space="preserve">OVR と人気の双方で団体を支えた二人の在位は、{eraTag}そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9535,19 +9535,19 @@
       </c>
       <c r="E291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionB[2]</t>
+          <t xml:space="preserve">sectionC[1]</t>
         </is>
       </c>
       <c r="H291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{eraTag}と呼ばれるこの章で、{surname1}と{surname2}はそれぞれ別の頂点を立てた。</t>
+          <t xml:space="preserve">二人が走り抜けた後、次章の主役{nextChapterTopSurname}が立ち上がる足場ができていた。</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionB[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9567,19 +9567,19 @@
       </c>
       <c r="E292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionB[3]</t>
+          <t xml:space="preserve">sectionC[2]</t>
         </is>
       </c>
       <c r="H292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR と人気の双方で団体を支えた二人の在位は、{eraTag}そのものだった。</t>
+          <t xml:space="preserve">{surname1}と{surname2}が並走した時代の余熱は、{risingPeerSurname}ら次世代に継がれた。</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[3]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9599,19 +9599,19 @@
       </c>
       <c r="E293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionC[1]</t>
+          <t xml:space="preserve">sectionC[3]</t>
         </is>
       </c>
       <c r="H293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人が走り抜けた後、次章の主役{nextChapterTopSurname}が立ち上がる足場ができていた。</t>
+          <t xml:space="preserve">二つの頂が並んだこの章が閉じるとき、団体には{successorStyle}を継ぐ若手の影が伸び始めていた。</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionA[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9626,24 +9626,24 @@
       </c>
       <c r="D294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionC[2]</t>
+          <t xml:space="preserve">peakDefender.sectionA[1]</t>
         </is>
       </c>
       <c r="H294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname1}と{surname2}が並走した時代の余熱は、{risingPeerSurname}ら次世代に継がれた。</t>
+          <t xml:space="preserve">{surname}はこの章を通じて王座を{defenses}度防衛した。{topRivalClause}{topVenueClause}</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL.sectionC[3]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionA[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9658,24 +9658,24 @@
       </c>
       <c r="D295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_DUAL</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sectionC[3]</t>
+          <t xml:space="preserve">peakDefender.sectionA[2]</t>
         </is>
       </c>
       <c r="H295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二つの頂が並んだこの章が閉じるとき、団体には{successorStyle}を継ぐ若手の影が伸び始めていた。</t>
+          <t xml:space="preserve">{titleReigns}度の戴冠、{defenses}度の防衛——{surname}は挑戦者を退け続けた。{warClause}</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionB[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9695,19 +9695,19 @@
       </c>
       <c r="E296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionA[1]</t>
+          <t xml:space="preserve">peakDefender.sectionB[1]</t>
         </is>
       </c>
       <c r="H296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}はこの章を通じて王座を{defenses}度防衛した。{topRivalClause}{topVenueClause}</t>
+          <t xml:space="preserve">{surname}が{styleJa}で団体を引っ張った時期、{org}全体の試合運びには{spiritAxis}の色が濃く染み込んでいった。</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionB[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9727,19 +9727,19 @@
       </c>
       <c r="E297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionA[2]</t>
+          <t xml:space="preserve">peakDefender.sectionB[2]</t>
         </is>
       </c>
       <c r="H297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{titleReigns}度の戴冠、{defenses}度の防衛——{surname}は挑戦者を退け続けた。{warClause}</t>
+          <t xml:space="preserve">OVR{peakOVR}・人気{peakPop}に達したこの選手の在位は、{eraTag}と呼ぶに相応しい時代を作った。</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionC[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9759,19 +9759,19 @@
       </c>
       <c r="E298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionB[1]</t>
+          <t xml:space="preserve">peakDefender.sectionC[1]</t>
         </is>
       </c>
       <c r="H298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が{styleJa}で団体を引っ張った時期、{org}全体の試合運びには{spiritAxis}の色が濃く染み込んでいった。</t>
+          <t xml:space="preserve">{surname}が見せた{styleJa}は、{risingClause}次章の主役{nextChapterTopSurname}が立ち上がる足場は、確かにこの世代に築かれていた。</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionC[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9791,19 +9791,19 @@
       </c>
       <c r="E299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionB[2]</t>
+          <t xml:space="preserve">peakDefender.sectionC[2]</t>
         </is>
       </c>
       <c r="H299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR{peakOVR}・人気{peakPop}に達したこの選手の在位は、{eraTag}と呼ぶに相応しい時代を作った。</t>
+          <t xml:space="preserve">{surname}の章が閉じるとき、団体には{successorStyle}を継ぐ若手の影が既に伸び始めていた。</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionA[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9823,19 +9823,19 @@
       </c>
       <c r="E300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionC[1]</t>
+          <t xml:space="preserve">defender.sectionA[1]</t>
         </is>
       </c>
       <c r="H300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が見せた{styleJa}は、{risingClause}次章の主役{nextChapterTopSurname}が立ち上がる足場は、確かにこの世代に築かれていた。</t>
+          <t xml:space="preserve">{surname}は王座を{defenses}度防衛し、{titleReigns}度の戴冠と合わせて団体の核を担った。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.peakDefender.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionA[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9855,19 +9855,19 @@
       </c>
       <c r="E301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">peakDefender.sectionC[2]</t>
+          <t xml:space="preserve">defender.sectionA[2]</t>
         </is>
       </c>
       <c r="H301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章が閉じるとき、団体には{successorStyle}を継ぐ若手の影が既に伸び始めていた。</t>
+          <t xml:space="preserve">{surname}が立っていることが、団体の安定そのものだった。挑戦者たちはなかなか手が届かなかった。{warClause}</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionB[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9887,19 +9887,19 @@
       </c>
       <c r="E302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionA[1]</t>
+          <t xml:space="preserve">defender.sectionB[1]</t>
         </is>
       </c>
       <c r="H302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は王座を{defenses}度防衛し、{titleReigns}度の戴冠と合わせて団体の核を担った。{topRivalClause}</t>
+          <t xml:space="preserve">{surname}の{styleJa}は、この章の{org}を{spiritAxis}に染め上げた。</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionB[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9919,19 +9919,19 @@
       </c>
       <c r="E303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionA[2]</t>
+          <t xml:space="preserve">defender.sectionB[2]</t>
         </is>
       </c>
       <c r="H303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が立っていることが、団体の安定そのものだった。挑戦者たちはなかなか手が届かなかった。{warClause}</t>
+          <t xml:space="preserve">{eraTag}と呼ばれるこの時代、戴冠者の名前を聞かれれば誰もが{surname}の名を挙げた。</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionC[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9951,19 +9951,19 @@
       </c>
       <c r="E304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionB[1]</t>
+          <t xml:space="preserve">defender.sectionC[1]</t>
         </is>
       </c>
       <c r="H304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の{styleJa}は、この章の{org}を{spiritAxis}に染め上げた。</t>
+          <t xml:space="preserve">{risingClause}{surname}の積み上げた防衛は、後進にとっての到達目標になった。</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionC[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -9983,19 +9983,19 @@
       </c>
       <c r="E305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionB[2]</t>
+          <t xml:space="preserve">defender.sectionC[2]</t>
         </is>
       </c>
       <c r="H305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{eraTag}と呼ばれるこの時代、戴冠者の名前を聞かれれば誰もが{surname}の名を挙げた。</t>
+          <t xml:space="preserve">{nextChapterTopSurname}が立つ前提として、{surname}が築いた地盤があった。</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionA[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10015,19 +10015,19 @@
       </c>
       <c r="E306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionC[1]</t>
+          <t xml:space="preserve">champion.sectionA[1]</t>
         </is>
       </c>
       <c r="H306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{risingClause}{surname}の積み上げた防衛は、後進にとっての到達目標になった。</t>
+          <t xml:space="preserve">{surname}は{titleReigns}度の戴冠を重ね、この章の主役を担った。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.defender.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionA[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10047,19 +10047,19 @@
       </c>
       <c r="E307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.sectionC[2]</t>
+          <t xml:space="preserve">champion.sectionA[2]</t>
         </is>
       </c>
       <c r="H307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nextChapterTopSurname}が立つ前提として、{surname}が築いた地盤があった。</t>
+          <t xml:space="preserve">何度王座から落ちても、{surname}は戻ってきた。{titleReigns}度の戴冠はその粘りの証だった。{warClause}</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionB[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10079,19 +10079,19 @@
       </c>
       <c r="E308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionA[1]</t>
+          <t xml:space="preserve">champion.sectionB[1]</t>
         </is>
       </c>
       <c r="H308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{titleReigns}度の戴冠を重ね、この章の主役を担った。{topRivalClause}</t>
+          <t xml:space="preserve">{surname}を中心に、{org}は{spiritAxis}の色を強めた章だった。</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionB[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10111,19 +10111,19 @@
       </c>
       <c r="E309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionA[2]</t>
+          <t xml:space="preserve">champion.sectionB[2]</t>
         </is>
       </c>
       <c r="H309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度王座から落ちても、{surname}は戻ってきた。{titleReigns}度の戴冠はその粘りの証だった。{warClause}</t>
+          <t xml:space="preserve">OVR{peakOVR}の{surname}が立った時代、それは{eraTag}に他ならなかった。</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionC[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10143,19 +10143,19 @@
       </c>
       <c r="E310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionB[1]</t>
+          <t xml:space="preserve">champion.sectionC[1]</t>
         </is>
       </c>
       <c r="H310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}を中心に、{org}は{spiritAxis}の色を強めた章だった。</t>
+          <t xml:space="preserve">{surname}が背中で見せた挑み続ける姿勢は、{risingPeerSurname}たち次世代の選手に受け継がれた。</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionC[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10175,19 +10175,19 @@
       </c>
       <c r="E311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionB[2]</t>
+          <t xml:space="preserve">champion.sectionC[2]</t>
         </is>
       </c>
       <c r="H311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR{peakOVR}の{surname}が立った時代、それは{eraTag}に他ならなかった。</t>
+          <t xml:space="preserve">{nextChapterTopSurname}の足場は、この章の{surname}の戴冠の積み重ねの上に立った。</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionA[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10207,19 +10207,19 @@
       </c>
       <c r="E312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionC[1]</t>
+          <t xml:space="preserve">popStar.sectionA[1]</t>
         </is>
       </c>
       <c r="H312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が背中で見せた挑み続ける姿勢は、{risingPeerSurname}たち次世代の選手に受け継がれた。</t>
+          <t xml:space="preserve">{surname}の人気が客足を支えた。戦績ではなく動員で、時代を作った世代だった。{topVenueClause}</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.champion.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionA[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10239,19 +10239,19 @@
       </c>
       <c r="E313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.sectionC[2]</t>
+          <t xml:space="preserve">popStar.sectionA[2]</t>
         </is>
       </c>
       <c r="H313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nextChapterTopSurname}の足場は、この章の{surname}の戴冠の積み重ねの上に立った。</t>
+          <t xml:space="preserve">王座にこそ恵まれなかったが、{surname}の華やかさが客席を埋めた。</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionB[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10271,19 +10271,19 @@
       </c>
       <c r="E314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionA[1]</t>
+          <t xml:space="preserve">popStar.sectionB[1]</t>
         </is>
       </c>
       <c r="H314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の人気が客足を支えた。戦績ではなく動員で、時代を作った世代だった。{topVenueClause}</t>
+          <t xml:space="preserve">人気{peakPop}を記録したこの選手は、{org}にとってチケットそのものだった。</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionB[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10303,19 +10303,19 @@
       </c>
       <c r="E315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionA[2]</t>
+          <t xml:space="preserve">popStar.sectionB[2]</t>
         </is>
       </c>
       <c r="H315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座にこそ恵まれなかったが、{surname}の華やかさが客席を埋めた。</t>
+          <t xml:space="preserve">試合記録には残らない記憶というものを、{surname}は、その人気でこの世代に刻みつけた。</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionC[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10335,19 +10335,19 @@
       </c>
       <c r="E316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionB[1]</t>
+          <t xml:space="preserve">popStar.sectionC[1]</t>
         </is>
       </c>
       <c r="H316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">人気{peakPop}を記録したこの選手は、{org}にとってチケットそのものだった。</t>
+          <t xml:space="preserve">{surname}が築いた華やぎの記憶は、{risingPeerSurname}たち次世代の客寄せにも引き継がれた。</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionC[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10367,19 +10367,19 @@
       </c>
       <c r="E317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionB[2]</t>
+          <t xml:space="preserve">popStar.sectionC[2]</t>
         </is>
       </c>
       <c r="H317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合記録には残らない記憶というものを、{surname}は、その人気でこの世代に刻みつけた。</t>
+          <t xml:space="preserve">{surname}が会場を埋めた時代の余熱は、次の章の{nextChapterTopSurname}の入場にも残っていた。</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionA[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10399,19 +10399,19 @@
       </c>
       <c r="E318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionC[1]</t>
+          <t xml:space="preserve">generationShift.sectionA[1]</t>
         </is>
       </c>
       <c r="H318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が築いた華やぎの記憶は、{risingPeerSurname}たち次世代の客寄せにも引き継がれた。</t>
+          <t xml:space="preserve">{surname}は前世代の主役たちと並走し、世代交代の橋渡しとなった。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.popStar.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionA[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10431,19 +10431,19 @@
       </c>
       <c r="E319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">popStar.sectionC[2]</t>
+          <t xml:space="preserve">generationShift.sectionA[2]</t>
         </is>
       </c>
       <c r="H319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が会場を埋めた時代の余熱は、次の章の{nextChapterTopSurname}の入場にも残っていた。</t>
+          <t xml:space="preserve">前章の主役たちが退いていく中、{surname}が次の中心を担った。</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionB[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10463,19 +10463,19 @@
       </c>
       <c r="E320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionA[1]</t>
+          <t xml:space="preserve">generationShift.sectionB[1]</t>
         </is>
       </c>
       <c r="H320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は前世代の主役たちと並走し、世代交代の橋渡しとなった。{topRivalClause}</t>
+          <t xml:space="preserve">{surname}の章は、過去と未来が混じり合った時間として{org}史に残る。{eraTag}と呼ぶには複雑な時代だった。</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionB[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10495,19 +10495,19 @@
       </c>
       <c r="E321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionA[2]</t>
+          <t xml:space="preserve">generationShift.sectionB[2]</t>
         </is>
       </c>
       <c r="H321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前章の主役たちが退いていく中、{surname}が次の中心を担った。</t>
+          <t xml:space="preserve">{spiritAxis}の地力を保ったまま、団体は次世代へと足場を移し始めていた。</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionC[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10527,19 +10527,19 @@
       </c>
       <c r="E322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionB[1]</t>
+          <t xml:space="preserve">generationShift.sectionC[1]</t>
         </is>
       </c>
       <c r="H322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章は、過去と未来が混じり合った時間として{org}史に残る。{eraTag}と呼ぶには複雑な時代だった。</t>
+          <t xml:space="preserve">{risingClause}{surname}が橋渡した先に、次章の{nextChapterTopSurname}が立った。</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionC[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10559,19 +10559,19 @@
       </c>
       <c r="E323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionB[2]</t>
+          <t xml:space="preserve">generationShift.sectionC[2]</t>
         </is>
       </c>
       <c r="H323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{spiritAxis}の地力を保ったまま、団体は次世代へと足場を移し始めていた。</t>
+          <t xml:space="preserve">{surname}が古参と新参の間に立った時間は、団体の世代の連続性そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionA[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10591,19 +10591,19 @@
       </c>
       <c r="E324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionC[1]</t>
+          <t xml:space="preserve">struggle.sectionA[1]</t>
         </is>
       </c>
       <c r="H324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{risingClause}{surname}が橋渡した先に、次章の{nextChapterTopSurname}が立った。</t>
+          <t xml:space="preserve">{surname}は{styleJa}を貫いたが、上位の壁は厚かった。届かないまま章は閉じる。{warClause}</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.generationShift.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionA[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10623,19 +10623,19 @@
       </c>
       <c r="E325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generationShift.sectionC[2]</t>
+          <t xml:space="preserve">struggle.sectionA[2]</t>
         </is>
       </c>
       <c r="H325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が古参と新参の間に立った時間は、団体の世代の連続性そのものだった。</t>
+          <t xml:space="preserve">挑んでは敗れ、それでも{surname}は{styleJa}を捨てなかった。</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionB[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10655,19 +10655,19 @@
       </c>
       <c r="E326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionA[1]</t>
+          <t xml:space="preserve">struggle.sectionB[1]</t>
         </is>
       </c>
       <c r="H326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{styleJa}を貫いたが、上位の壁は厚かった。届かないまま章は閉じる。{warClause}</t>
+          <t xml:space="preserve">{surname}の章は、勝てなかった日々の記録である。だが、それでも諦めず挑戦を続けた日々の記録でもある。</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionB[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10687,19 +10687,19 @@
       </c>
       <c r="E327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionA[2]</t>
+          <t xml:space="preserve">struggle.sectionB[2]</t>
         </is>
       </c>
       <c r="H327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑んでは敗れ、それでも{surname}は{styleJa}を捨てなかった。</t>
+          <t xml:space="preserve">届かなかった世代の象徴として、{surname}は{org}の地力に深い陰影を残した。</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionC[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10719,19 +10719,19 @@
       </c>
       <c r="E328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionB[1]</t>
+          <t xml:space="preserve">struggle.sectionC[1]</t>
         </is>
       </c>
       <c r="H328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の章は、勝てなかった日々の記録である。だが、それでも諦めず挑戦を続けた日々の記録でもある。</t>
+          <t xml:space="preserve">{surname}が届かなかった頂は、{risingPeerSurname}ら次世代の目標として残された。</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionC[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10751,19 +10751,19 @@
       </c>
       <c r="E329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionB[2]</t>
+          <t xml:space="preserve">struggle.sectionC[2]</t>
         </is>
       </c>
       <c r="H329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">届かなかった世代の象徴として、{surname}は{org}の地力に深い陰影を残した。</t>
+          <t xml:space="preserve">{nextChapterTopSurname}が登る山は、{surname}が手を伸ばし続けた山だった。</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionA[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10783,19 +10783,19 @@
       </c>
       <c r="E330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionC[1]</t>
+          <t xml:space="preserve">craftsman.sectionA[1]</t>
         </is>
       </c>
       <c r="H330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が届かなかった頂は、{risingPeerSurname}ら次世代の目標として残された。</t>
+          <t xml:space="preserve">{surname}は{styleJa}を武器に団体を支えた。王座にこそ届かなかったが、世代の支柱だった。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.struggle.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionA[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10815,19 +10815,19 @@
       </c>
       <c r="E331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">struggle.sectionC[2]</t>
+          <t xml:space="preserve">craftsman.sectionA[2]</t>
         </is>
       </c>
       <c r="H331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nextChapterTopSurname}が登る山は、{surname}が手を伸ばし続けた山だった。</t>
+          <t xml:space="preserve">OVR{peakOVR}に達した{surname}は、無冠ながら誰よりも信頼される選手だった。</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionB[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10847,19 +10847,19 @@
       </c>
       <c r="E332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman.sectionA[1]</t>
+          <t xml:space="preserve">craftsman.sectionB[1]</t>
         </is>
       </c>
       <c r="H332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は{styleJa}を武器に団体を支えた。王座にこそ届かなかったが、世代の支柱だった。{topRivalClause}</t>
+          <t xml:space="preserve">{surname}の{styleJa}は派手さこそないが、{org}を底から支え続けた。</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionB[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10879,19 +10879,19 @@
       </c>
       <c r="E333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman.sectionA[2]</t>
+          <t xml:space="preserve">craftsman.sectionB[2]</t>
         </is>
       </c>
       <c r="H333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">OVR{peakOVR}に達した{surname}は、無冠ながら誰よりも信頼される選手だった。</t>
+          <t xml:space="preserve">王座とは縁がなかったが、{surname}の{styleJa}はこの章の地力そのものだった。</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionC[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10911,19 +10911,19 @@
       </c>
       <c r="E334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman.sectionB[1]</t>
+          <t xml:space="preserve">craftsman.sectionC[1]</t>
         </is>
       </c>
       <c r="H334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}の{styleJa}は派手さこそないが、{org}を底から支え続けた。</t>
+          <t xml:space="preserve">{surname}が継いだ{styleJa}の系譜は、{risingPeerSurname}ら次世代にも残った。</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionC[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10943,19 +10943,19 @@
       </c>
       <c r="E335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman.sectionB[2]</t>
+          <t xml:space="preserve">craftsman.sectionC[2]</t>
         </is>
       </c>
       <c r="H335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座とは縁がなかったが、{surname}の{styleJa}はこの章の地力そのものだった。</t>
+          <t xml:space="preserve">{nextChapterTopSurname}が前に出るとき、その背後には{surname}の積み上げた{styleJa}があった。</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionC[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionA[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10975,19 +10975,19 @@
       </c>
       <c r="E336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman.sectionC[1]</t>
+          <t xml:space="preserve">uncrowned.sectionA[1]</t>
         </is>
       </c>
       <c r="H336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}が継いだ{styleJa}の系譜は、{risingPeerSurname}ら次世代にも残った。</t>
+          <t xml:space="preserve">{surname}は無冠ながらこの世代の主役だった。タイトルでは測れない存在感がそこにあった。{topRivalClause}</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.craftsman.sectionC[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionA[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11007,19 +11007,19 @@
       </c>
       <c r="E337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">craftsman.sectionC[2]</t>
+          <t xml:space="preserve">uncrowned.sectionA[2]</t>
         </is>
       </c>
       <c r="H337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nextChapterTopSurname}が前に出るとき、その背後には{surname}の積み上げた{styleJa}があった。</t>
+          <t xml:space="preserve">王座を獲ることはなかったが、{surname}抜きにこの章は語れない。</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionA[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionB[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11039,19 +11039,19 @@
       </c>
       <c r="E338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned.sectionA[1]</t>
+          <t xml:space="preserve">uncrowned.sectionB[1]</t>
         </is>
       </c>
       <c r="H338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は無冠ながらこの世代の主役だった。タイトルでは測れない存在感がそこにあった。{topRivalClause}</t>
+          <t xml:space="preserve">{surname}は最後までベルトを巻かなかった。だが{org}史はこの選手を主役として記憶する。</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionA[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionB[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11071,19 +11071,19 @@
       </c>
       <c r="E339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned.sectionA[2]</t>
+          <t xml:space="preserve">uncrowned.sectionB[2]</t>
         </is>
       </c>
       <c r="H339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座を獲ることはなかったが、{surname}抜きにこの章は語れない。</t>
+          <t xml:space="preserve">記録には残らないが、記憶には深く残る。{surname}はそういう世代の主役だった。</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionB[1]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionC[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11103,19 +11103,19 @@
       </c>
       <c r="E340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned.sectionB[1]</t>
+          <t xml:space="preserve">uncrowned.sectionC[1]</t>
         </is>
       </c>
       <c r="H340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{surname}は最後までベルトを巻かなかった。だが{org}史はこの選手を主役として記憶する。</t>
+          <t xml:space="preserve">{risingClause}{surname}の存在感は、無冠であることの強さとして次世代に伝わった。</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionB[2]</t>
+          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionC[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11135,81 +11135,17 @@
       </c>
       <c r="E341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">uncrowned.sectionB[2]</t>
+          <t xml:space="preserve">uncrowned.sectionC[2]</t>
         </is>
       </c>
       <c r="H341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">記録には残らないが、記憶には深く残る。{surname}はそういう世代の主役だった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="40" customHeight="1">
-      <c r="A342" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionC[1]</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">称号・記録・年代記</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">uncrowned.sectionC[1]</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{risingClause}{surname}の存在感は、無冠であることの強さとして次世代に伝わった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="40" customHeight="1">
-      <c r="A343" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2.uncrowned.sectionC[2]</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">称号・記録・年代記</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/management.js</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Engine.chronicle.QUOTE_TEMPLATES_V2</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">uncrowned.sectionC[2]</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">{nextChapterTopSurname}が王座を獲るとき、{surname}が残した「無冠の重み」が背後に静かに横たわっていた。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J343"/>
+  <autoFilter ref="A1:J341"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
